--- a/research/traditional_assets/database/data/ireland/ireland_r_e_i_t.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_r_e_i_t.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07153891332286741</v>
+        <v>0.07148886468121383</v>
       </c>
       <c r="C2">
-        <v>1138.563623911787</v>
+        <v>1128.630468007363</v>
       </c>
       <c r="D2">
-        <v>1131.923623911787</v>
+        <v>1133.172468007363</v>
       </c>
       <c r="E2">
-        <v>-619.3</v>
+        <v>-608.1179999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.182</v>
       </c>
       <c r="G2">
         <v>6.64</v>
@@ -1445,28 +1445,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5624545999999999</v>
       </c>
       <c r="N2">
-        <v>75.68066666666667</v>
+        <v>75.11821206666667</v>
       </c>
       <c r="O2">
-        <v>9.460083333333333</v>
+        <v>9.389776508333334</v>
       </c>
       <c r="P2">
-        <v>66.22058333333334</v>
+        <v>65.72843555833333</v>
       </c>
       <c r="Q2">
-        <v>66.80658333333334</v>
+        <v>66.31443555833333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07153891332286741</v>
+        <v>0.07176640371839782</v>
       </c>
       <c r="T2">
-        <v>0.5016993284768604</v>
+        <v>0.5061335397133984</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>134.5542674318366</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07148886468121383</v>
+        <v>0.07143881603956025</v>
       </c>
       <c r="C3">
-        <v>1128.630468007363</v>
+        <v>1118.700070830033</v>
       </c>
       <c r="D3">
-        <v>1133.172468007363</v>
+        <v>1134.424070830033</v>
       </c>
       <c r="E3">
-        <v>-608.1179999999999</v>
+        <v>-596.9359999999999</v>
       </c>
       <c r="F3">
-        <v>11.182</v>
+        <v>22.364</v>
       </c>
       <c r="G3">
         <v>6.64</v>
@@ -1527,28 +1527,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M3">
-        <v>0.5624545999999999</v>
+        <v>1.1249092</v>
       </c>
       <c r="N3">
-        <v>75.11821206666667</v>
+        <v>74.55575746666666</v>
       </c>
       <c r="O3">
-        <v>9.389776508333334</v>
+        <v>9.319469683333333</v>
       </c>
       <c r="P3">
-        <v>65.72843555833333</v>
+        <v>65.23628778333332</v>
       </c>
       <c r="Q3">
-        <v>66.31443555833333</v>
+        <v>65.82228778333332</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07176640371839782</v>
+        <v>0.07199853677506148</v>
       </c>
       <c r="T3">
-        <v>0.5061335397133984</v>
+        <v>0.5106582450568042</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>134.5542674318366</v>
+        <v>67.2771337159183</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07143881603956025</v>
+        <v>0.07138876739790666</v>
       </c>
       <c r="C4">
-        <v>1118.700070830033</v>
+        <v>1108.772441531049</v>
       </c>
       <c r="D4">
-        <v>1134.424070830033</v>
+        <v>1135.678441531049</v>
       </c>
       <c r="E4">
-        <v>-596.9359999999999</v>
+        <v>-585.7539999999999</v>
       </c>
       <c r="F4">
-        <v>22.364</v>
+        <v>33.54599999999999</v>
       </c>
       <c r="G4">
         <v>6.64</v>
@@ -1609,28 +1609,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M4">
-        <v>1.1249092</v>
+        <v>1.6873638</v>
       </c>
       <c r="N4">
-        <v>74.55575746666666</v>
+        <v>73.99330286666667</v>
       </c>
       <c r="O4">
-        <v>9.319469683333333</v>
+        <v>9.249162858333333</v>
       </c>
       <c r="P4">
-        <v>65.23628778333332</v>
+        <v>64.74414000833333</v>
       </c>
       <c r="Q4">
-        <v>65.82228778333332</v>
+        <v>65.33014000833333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07199853677506148</v>
+        <v>0.07223545608031615</v>
       </c>
       <c r="T4">
-        <v>0.5106582450568042</v>
+        <v>0.5152762432938888</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.2771337159183</v>
+        <v>44.85142247727887</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07138876739790666</v>
+        <v>0.07133871875625308</v>
       </c>
       <c r="C5">
-        <v>1108.772441531049</v>
+        <v>1098.84758930218</v>
       </c>
       <c r="D5">
-        <v>1135.678441531049</v>
+        <v>1136.93558930218</v>
       </c>
       <c r="E5">
-        <v>-585.7539999999999</v>
+        <v>-574.572</v>
       </c>
       <c r="F5">
-        <v>33.54599999999999</v>
+        <v>44.72799999999999</v>
       </c>
       <c r="G5">
         <v>6.64</v>
@@ -1691,28 +1691,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M5">
-        <v>1.6873638</v>
+        <v>2.2498184</v>
       </c>
       <c r="N5">
-        <v>73.99330286666667</v>
+        <v>73.43084826666667</v>
       </c>
       <c r="O5">
-        <v>9.249162858333333</v>
+        <v>9.178856033333334</v>
       </c>
       <c r="P5">
-        <v>64.74414000833333</v>
+        <v>64.25199223333334</v>
       </c>
       <c r="Q5">
-        <v>65.33014000833333</v>
+        <v>64.83799223333334</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07223545608031615</v>
+        <v>0.07247731120443029</v>
       </c>
       <c r="T5">
-        <v>0.5152762432938888</v>
+        <v>0.5199904498275792</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.85142247727887</v>
+        <v>33.63856685795915</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07133871875625308</v>
+        <v>0.07128867011459948</v>
       </c>
       <c r="C6">
-        <v>1098.84758930218</v>
+        <v>1088.925523375946</v>
       </c>
       <c r="D6">
-        <v>1136.93558930218</v>
+        <v>1138.195523375946</v>
       </c>
       <c r="E6">
-        <v>-574.572</v>
+        <v>-563.39</v>
       </c>
       <c r="F6">
-        <v>44.72799999999999</v>
+        <v>55.91</v>
       </c>
       <c r="G6">
         <v>6.64</v>
@@ -1773,28 +1773,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M6">
-        <v>2.2498184</v>
+        <v>2.812273</v>
       </c>
       <c r="N6">
-        <v>73.43084826666667</v>
+        <v>72.86839366666666</v>
       </c>
       <c r="O6">
-        <v>9.178856033333334</v>
+        <v>9.108549208333333</v>
       </c>
       <c r="P6">
-        <v>64.25199223333334</v>
+        <v>63.75984445833333</v>
       </c>
       <c r="Q6">
-        <v>64.83799223333334</v>
+        <v>64.34584445833333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07247731120443029</v>
+        <v>0.07272425801536789</v>
       </c>
       <c r="T6">
-        <v>0.5199904498275792</v>
+        <v>0.5248039028146105</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.63856685795915</v>
+        <v>26.91085348636732</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07128867011459948</v>
+        <v>0.07123862147294589</v>
       </c>
       <c r="C7">
-        <v>1088.925523375946</v>
+        <v>1079.006253025829</v>
       </c>
       <c r="D7">
-        <v>1138.195523375946</v>
+        <v>1139.458253025829</v>
       </c>
       <c r="E7">
-        <v>-563.39</v>
+        <v>-552.208</v>
       </c>
       <c r="F7">
-        <v>55.91</v>
+        <v>67.092</v>
       </c>
       <c r="G7">
         <v>6.64</v>
@@ -1855,28 +1855,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M7">
-        <v>2.812273</v>
+        <v>3.3747276</v>
       </c>
       <c r="N7">
-        <v>72.86839366666666</v>
+        <v>72.30593906666667</v>
       </c>
       <c r="O7">
-        <v>9.108549208333333</v>
+        <v>9.038242383333333</v>
       </c>
       <c r="P7">
-        <v>63.75984445833333</v>
+        <v>63.26769668333333</v>
       </c>
       <c r="Q7">
-        <v>64.34584445833333</v>
+        <v>63.85369668333333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07272425801536789</v>
+        <v>0.07297645901377224</v>
       </c>
       <c r="T7">
-        <v>0.5248039028146105</v>
+        <v>0.5297197696949829</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.91085348636732</v>
+        <v>22.42571123863943</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07123862147294589</v>
+        <v>0.07118857283129232</v>
       </c>
       <c r="C8">
-        <v>1079.006253025829</v>
+        <v>1069.089787566515</v>
       </c>
       <c r="D8">
-        <v>1139.458253025829</v>
+        <v>1140.723787566515</v>
       </c>
       <c r="E8">
-        <v>-552.208</v>
+        <v>-541.026</v>
       </c>
       <c r="F8">
-        <v>67.09199999999998</v>
+        <v>78.27399999999997</v>
       </c>
       <c r="G8">
         <v>6.64</v>
@@ -1937,28 +1937,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M8">
-        <v>3.374727599999999</v>
+        <v>3.937182199999998</v>
       </c>
       <c r="N8">
-        <v>72.30593906666667</v>
+        <v>71.74348446666667</v>
       </c>
       <c r="O8">
-        <v>9.038242383333333</v>
+        <v>8.967935558333334</v>
       </c>
       <c r="P8">
-        <v>63.26769668333333</v>
+        <v>62.77554890833333</v>
       </c>
       <c r="Q8">
-        <v>63.85369668333333</v>
+        <v>63.36154890833333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07297645901377224</v>
+        <v>0.07323408368956164</v>
       </c>
       <c r="T8">
-        <v>0.5297197696949829</v>
+        <v>0.5347413541426751</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.42571123863943</v>
+        <v>19.22203820454809</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07118857283129232</v>
+        <v>0.07113852418963874</v>
       </c>
       <c r="C9">
-        <v>1069.089787566515</v>
+        <v>1059.176136354118</v>
       </c>
       <c r="D9">
-        <v>1140.723787566515</v>
+        <v>1141.992136354118</v>
       </c>
       <c r="E9">
-        <v>-541.026</v>
+        <v>-529.8439999999999</v>
       </c>
       <c r="F9">
-        <v>78.274</v>
+        <v>89.45599999999999</v>
       </c>
       <c r="G9">
         <v>6.64</v>
@@ -2019,28 +2019,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M9">
-        <v>3.9371822</v>
+        <v>4.499636799999999</v>
       </c>
       <c r="N9">
-        <v>71.74348446666667</v>
+        <v>71.18102986666666</v>
       </c>
       <c r="O9">
-        <v>8.967935558333334</v>
+        <v>8.897628733333333</v>
       </c>
       <c r="P9">
-        <v>62.77554890833333</v>
+        <v>62.28340113333333</v>
       </c>
       <c r="Q9">
-        <v>63.36154890833333</v>
+        <v>62.86940113333333</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07323408368956164</v>
+        <v>0.07349730890178124</v>
       </c>
       <c r="T9">
-        <v>0.5347413541426751</v>
+        <v>0.5398721034696651</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.22203820454808</v>
+        <v>16.81928342897957</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07113852418963874</v>
+        <v>0.07108847554798514</v>
       </c>
       <c r="C10">
-        <v>1059.176136354118</v>
+        <v>1049.265308786406</v>
       </c>
       <c r="D10">
-        <v>1141.992136354118</v>
+        <v>1143.263308786406</v>
       </c>
       <c r="E10">
-        <v>-529.8439999999999</v>
+        <v>-518.662</v>
       </c>
       <c r="F10">
-        <v>89.45599999999999</v>
+        <v>100.638</v>
       </c>
       <c r="G10">
         <v>6.64</v>
@@ -2101,28 +2101,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M10">
-        <v>4.499636799999999</v>
+        <v>5.062091399999999</v>
       </c>
       <c r="N10">
-        <v>71.18102986666666</v>
+        <v>70.61857526666667</v>
       </c>
       <c r="O10">
-        <v>8.897628733333333</v>
+        <v>8.827321908333333</v>
       </c>
       <c r="P10">
-        <v>62.28340113333333</v>
+        <v>61.79125335833334</v>
       </c>
       <c r="Q10">
-        <v>62.86940113333333</v>
+        <v>62.37725335833333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07349730890178124</v>
+        <v>0.07376631928350016</v>
       </c>
       <c r="T10">
-        <v>0.5398721034696651</v>
+        <v>0.5451156165181271</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.81928342897957</v>
+        <v>14.95047415909296</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07108847554798514</v>
+        <v>0.07103842690633157</v>
       </c>
       <c r="C11">
-        <v>1049.265308786406</v>
+        <v>1039.357314303039</v>
       </c>
       <c r="D11">
-        <v>1143.263308786406</v>
+        <v>1144.537314303039</v>
       </c>
       <c r="E11">
-        <v>-518.662</v>
+        <v>-507.48</v>
       </c>
       <c r="F11">
-        <v>100.638</v>
+        <v>111.82</v>
       </c>
       <c r="G11">
         <v>6.64</v>
@@ -2183,28 +2183,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M11">
-        <v>5.062091399999999</v>
+        <v>5.624545999999999</v>
       </c>
       <c r="N11">
-        <v>70.61857526666667</v>
+        <v>70.05612066666667</v>
       </c>
       <c r="O11">
-        <v>8.827321908333333</v>
+        <v>8.757015083333334</v>
       </c>
       <c r="P11">
-        <v>61.79125335833334</v>
+        <v>61.29910558333334</v>
       </c>
       <c r="Q11">
-        <v>62.37725335833333</v>
+        <v>61.88510558333333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07376631928350016</v>
+        <v>0.07404130767370175</v>
       </c>
       <c r="T11">
-        <v>0.5451156165181271</v>
+        <v>0.5504756520787775</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.95047415909296</v>
+        <v>13.45542674318366</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07103842690633157</v>
+        <v>0.07113275326467798</v>
       </c>
       <c r="C12">
-        <v>1039.357314303039</v>
+        <v>1025.77656637653</v>
       </c>
       <c r="D12">
-        <v>1144.537314303039</v>
+        <v>1142.13856637653</v>
       </c>
       <c r="E12">
-        <v>-507.48</v>
+        <v>-496.298</v>
       </c>
       <c r="F12">
-        <v>111.82</v>
+        <v>123.002</v>
       </c>
       <c r="G12">
         <v>6.64</v>
@@ -2265,45 +2265,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M12">
-        <v>5.624546</v>
+        <v>6.371503599999999</v>
       </c>
       <c r="N12">
-        <v>70.05612066666667</v>
+        <v>69.30916306666667</v>
       </c>
       <c r="O12">
-        <v>8.757015083333334</v>
+        <v>8.663645383333334</v>
       </c>
       <c r="P12">
-        <v>61.29910558333334</v>
+        <v>60.64551768333334</v>
       </c>
       <c r="Q12">
-        <v>61.88510558333333</v>
+        <v>61.23151768333334</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07404130767370175</v>
+        <v>0.07432247557828987</v>
       </c>
       <c r="T12">
-        <v>0.5504756520787775</v>
+        <v>0.5559561378767456</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.45542674318366</v>
+        <v>11.87799166693819</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07113275326467798</v>
+        <v>0.07109582962302441</v>
       </c>
       <c r="C13">
-        <v>1025.77656637653</v>
+        <v>1015.53234721366</v>
       </c>
       <c r="D13">
-        <v>1142.13856637653</v>
+        <v>1143.07634721366</v>
       </c>
       <c r="E13">
-        <v>-496.298</v>
+        <v>-485.116</v>
       </c>
       <c r="F13">
-        <v>123.002</v>
+        <v>134.184</v>
       </c>
       <c r="G13">
         <v>6.64</v>
@@ -2347,28 +2347,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M13">
-        <v>6.371503599999999</v>
+        <v>6.950731199999998</v>
       </c>
       <c r="N13">
-        <v>69.30916306666667</v>
+        <v>68.72993546666667</v>
       </c>
       <c r="O13">
-        <v>8.663645383333334</v>
+        <v>8.591241933333334</v>
       </c>
       <c r="P13">
-        <v>60.64551768333334</v>
+        <v>60.13869353333334</v>
       </c>
       <c r="Q13">
-        <v>61.23151768333334</v>
+        <v>60.72469353333334</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07432247557828987</v>
+        <v>0.07461003366252773</v>
       </c>
       <c r="T13">
-        <v>0.5559561378767456</v>
+        <v>0.5615611801701221</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.87799166693819</v>
+        <v>10.88815902802668</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07109582962302441</v>
+        <v>0.07105890598137081</v>
       </c>
       <c r="C14">
-        <v>1015.53234721366</v>
+        <v>1005.289669292104</v>
       </c>
       <c r="D14">
-        <v>1143.07634721366</v>
+        <v>1144.015669292104</v>
       </c>
       <c r="E14">
-        <v>-485.116</v>
+        <v>-473.934</v>
       </c>
       <c r="F14">
-        <v>134.184</v>
+        <v>145.366</v>
       </c>
       <c r="G14">
         <v>6.64</v>
@@ -2429,28 +2429,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M14">
-        <v>6.950731199999998</v>
+        <v>7.529958799999999</v>
       </c>
       <c r="N14">
-        <v>68.72993546666667</v>
+        <v>68.15070786666666</v>
       </c>
       <c r="O14">
-        <v>8.591241933333334</v>
+        <v>8.518838483333333</v>
       </c>
       <c r="P14">
-        <v>60.13869353333334</v>
+        <v>59.63186938333333</v>
       </c>
       <c r="Q14">
-        <v>60.72469353333334</v>
+        <v>60.21786938333333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07461003366252773</v>
+        <v>0.07490420227743771</v>
       </c>
       <c r="T14">
-        <v>0.5615611801701221</v>
+        <v>0.5672950740104729</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.88815902802668</v>
+        <v>10.05060833356308</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07105890598137081</v>
+        <v>0.07123023233971723</v>
       </c>
       <c r="C15">
-        <v>1005.289669292104</v>
+        <v>989.7621854903753</v>
       </c>
       <c r="D15">
-        <v>1144.015669292104</v>
+        <v>1139.670185490375</v>
       </c>
       <c r="E15">
-        <v>-473.934</v>
+        <v>-462.752</v>
       </c>
       <c r="F15">
-        <v>145.366</v>
+        <v>156.548</v>
       </c>
       <c r="G15">
         <v>6.64</v>
@@ -2511,45 +2511,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M15">
-        <v>7.529958799999999</v>
+        <v>8.375318</v>
       </c>
       <c r="N15">
-        <v>68.15070786666666</v>
+        <v>67.30534866666667</v>
       </c>
       <c r="O15">
-        <v>8.518838483333333</v>
+        <v>8.413168583333334</v>
       </c>
       <c r="P15">
-        <v>59.63186938333333</v>
+        <v>58.89218008333334</v>
       </c>
       <c r="Q15">
-        <v>60.21786938333333</v>
+        <v>59.47818008333334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07490420227743771</v>
+        <v>0.07520521202292701</v>
       </c>
       <c r="T15">
-        <v>0.5672950740104729</v>
+        <v>0.5731623142192039</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.05060833356308</v>
+        <v>9.036154408306249</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07123023233971723</v>
+        <v>0.07120818369806366</v>
       </c>
       <c r="C16">
-        <v>989.7621854903753</v>
+        <v>979.1375705914415</v>
       </c>
       <c r="D16">
-        <v>1139.670185490375</v>
+        <v>1140.227570591441</v>
       </c>
       <c r="E16">
-        <v>-462.752</v>
+        <v>-451.5699999999999</v>
       </c>
       <c r="F16">
-        <v>156.548</v>
+        <v>167.73</v>
       </c>
       <c r="G16">
         <v>6.64</v>
@@ -2593,28 +2593,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M16">
-        <v>8.375318</v>
+        <v>8.973554999999999</v>
       </c>
       <c r="N16">
-        <v>67.30534866666667</v>
+        <v>66.70711166666666</v>
       </c>
       <c r="O16">
-        <v>8.413168583333334</v>
+        <v>8.338388958333333</v>
       </c>
       <c r="P16">
-        <v>58.89218008333334</v>
+        <v>58.36872270833333</v>
       </c>
       <c r="Q16">
-        <v>59.47818008333334</v>
+        <v>58.95472270833333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07520521202292701</v>
+        <v>0.07551330435066313</v>
       </c>
       <c r="T16">
-        <v>0.5731623142192039</v>
+        <v>0.5791676071387286</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.036154408306249</v>
+        <v>8.433744114419165</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07120818369806364</v>
+        <v>0.07118613505641007</v>
       </c>
       <c r="C17">
-        <v>979.1375705914418</v>
+        <v>968.5135011664081</v>
       </c>
       <c r="D17">
-        <v>1140.227570591442</v>
+        <v>1140.785501166408</v>
       </c>
       <c r="E17">
-        <v>-451.57</v>
+        <v>-440.388</v>
       </c>
       <c r="F17">
-        <v>167.73</v>
+        <v>178.912</v>
       </c>
       <c r="G17">
         <v>6.64</v>
@@ -2675,28 +2675,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M17">
-        <v>8.973554999999998</v>
+        <v>9.571791999999999</v>
       </c>
       <c r="N17">
-        <v>66.70711166666666</v>
+        <v>66.10887466666667</v>
       </c>
       <c r="O17">
-        <v>8.338388958333333</v>
+        <v>8.263609333333333</v>
       </c>
       <c r="P17">
-        <v>58.36872270833333</v>
+        <v>57.84526533333333</v>
       </c>
       <c r="Q17">
-        <v>58.95472270833333</v>
+        <v>58.43126533333333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07551330435066311</v>
+        <v>0.07582873221001199</v>
       </c>
       <c r="T17">
-        <v>0.5791676071387285</v>
+        <v>0.5853158832230039</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.433744114419166</v>
+        <v>7.906635107267967</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07118613505641007</v>
+        <v>0.07128308641475647</v>
       </c>
       <c r="C18">
-        <v>968.5135011664081</v>
+        <v>954.8822616755854</v>
       </c>
       <c r="D18">
-        <v>1140.785501166408</v>
+        <v>1138.336261675585</v>
       </c>
       <c r="E18">
-        <v>-440.388</v>
+        <v>-429.206</v>
       </c>
       <c r="F18">
-        <v>178.912</v>
+        <v>190.094</v>
       </c>
       <c r="G18">
         <v>6.64</v>
@@ -2757,45 +2757,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M18">
-        <v>9.571791999999999</v>
+        <v>10.3221042</v>
       </c>
       <c r="N18">
-        <v>66.10887466666667</v>
+        <v>65.35856246666667</v>
       </c>
       <c r="O18">
-        <v>8.263609333333333</v>
+        <v>8.169820308333334</v>
       </c>
       <c r="P18">
-        <v>57.84526533333333</v>
+        <v>57.18874215833333</v>
       </c>
       <c r="Q18">
-        <v>58.43126533333333</v>
+        <v>57.77474215833333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07582873221001199</v>
+        <v>0.07615176074067045</v>
       </c>
       <c r="T18">
-        <v>0.5853158832230039</v>
+        <v>0.5916123105382254</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.906635107267967</v>
+        <v>7.331902991898364</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07128308641475647</v>
+        <v>0.07126803777310289</v>
       </c>
       <c r="C19">
-        <v>954.8822616755854</v>
+        <v>944.0797391367206</v>
       </c>
       <c r="D19">
-        <v>1138.336261675585</v>
+        <v>1138.71573913672</v>
       </c>
       <c r="E19">
-        <v>-429.206</v>
+        <v>-418.024</v>
       </c>
       <c r="F19">
-        <v>190.094</v>
+        <v>201.276</v>
       </c>
       <c r="G19">
         <v>6.64</v>
@@ -2839,28 +2839,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M19">
-        <v>10.3221042</v>
+        <v>10.9292868</v>
       </c>
       <c r="N19">
-        <v>65.35856246666667</v>
+        <v>64.75137986666667</v>
       </c>
       <c r="O19">
-        <v>8.169820308333334</v>
+        <v>8.093922483333333</v>
       </c>
       <c r="P19">
-        <v>57.18874215833333</v>
+        <v>56.65745738333334</v>
       </c>
       <c r="Q19">
-        <v>57.77474215833333</v>
+        <v>57.24345738333334</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07615176074067045</v>
+        <v>0.07648266801597914</v>
       </c>
       <c r="T19">
-        <v>0.5916123105382254</v>
+        <v>0.5980623092513794</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.331902991898364</v>
+        <v>6.92457504790401</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07126803777310289</v>
+        <v>0.07125298913144931</v>
       </c>
       <c r="C20">
-        <v>944.0797391367206</v>
+        <v>933.277469688563</v>
       </c>
       <c r="D20">
-        <v>1138.71573913672</v>
+        <v>1139.095469688563</v>
       </c>
       <c r="E20">
-        <v>-418.024</v>
+        <v>-406.842</v>
       </c>
       <c r="F20">
-        <v>201.276</v>
+        <v>212.458</v>
       </c>
       <c r="G20">
         <v>6.64</v>
@@ -2921,28 +2921,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M20">
-        <v>10.9292868</v>
+        <v>11.5364694</v>
       </c>
       <c r="N20">
-        <v>64.75137986666667</v>
+        <v>64.14419726666667</v>
       </c>
       <c r="O20">
-        <v>8.093922483333333</v>
+        <v>8.018024658333333</v>
       </c>
       <c r="P20">
-        <v>56.65745738333334</v>
+        <v>56.12617260833333</v>
       </c>
       <c r="Q20">
-        <v>57.24345738333334</v>
+        <v>56.71217260833333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07648266801597914</v>
+        <v>0.07682174584129545</v>
       </c>
       <c r="T20">
-        <v>0.5980623092513794</v>
+        <v>0.6046715671920184</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.924575047904011</v>
+        <v>6.560123729593274</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07125298913144931</v>
+        <v>0.07123794048979573</v>
       </c>
       <c r="C21">
-        <v>933.277469688563</v>
+        <v>922.475453584393</v>
       </c>
       <c r="D21">
-        <v>1139.095469688563</v>
+        <v>1139.475453584393</v>
       </c>
       <c r="E21">
-        <v>-406.842</v>
+        <v>-395.66</v>
       </c>
       <c r="F21">
-        <v>212.458</v>
+        <v>223.64</v>
       </c>
       <c r="G21">
         <v>6.64</v>
@@ -3003,28 +3003,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M21">
-        <v>11.5364694</v>
+        <v>12.143652</v>
       </c>
       <c r="N21">
-        <v>64.14419726666667</v>
+        <v>63.53701466666666</v>
       </c>
       <c r="O21">
-        <v>8.018024658333333</v>
+        <v>7.942126833333333</v>
       </c>
       <c r="P21">
-        <v>56.12617260833333</v>
+        <v>55.59488783333333</v>
       </c>
       <c r="Q21">
-        <v>56.71217260833333</v>
+        <v>56.18088783333333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07682174584129545</v>
+        <v>0.07716930061224467</v>
       </c>
       <c r="T21">
-        <v>0.6046715671920184</v>
+        <v>0.6114460565811736</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.560123729593274</v>
+        <v>6.232117543113609</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07123794048979573</v>
+        <v>0.07140664184814213</v>
       </c>
       <c r="C22">
-        <v>922.475453584393</v>
+        <v>907.0481352974722</v>
       </c>
       <c r="D22">
-        <v>1139.475453584393</v>
+        <v>1135.230135297472</v>
       </c>
       <c r="E22">
-        <v>-395.66</v>
+        <v>-384.478</v>
       </c>
       <c r="F22">
-        <v>223.64</v>
+        <v>234.822</v>
       </c>
       <c r="G22">
         <v>6.64</v>
@@ -3085,45 +3085,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M22">
-        <v>12.143652</v>
+        <v>12.9856566</v>
       </c>
       <c r="N22">
-        <v>63.53701466666666</v>
+        <v>62.69501006666667</v>
       </c>
       <c r="O22">
-        <v>7.942126833333333</v>
+        <v>7.836876258333334</v>
       </c>
       <c r="P22">
-        <v>55.59488783333333</v>
+        <v>54.85813380833333</v>
       </c>
       <c r="Q22">
-        <v>56.18088783333333</v>
+        <v>55.44413380833333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07716930061224467</v>
+        <v>0.07752565423815461</v>
       </c>
       <c r="T22">
-        <v>0.6114460565811736</v>
+        <v>0.6183920520308137</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.232117543113609</v>
+        <v>5.828020022234893</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07140664184814213</v>
+        <v>0.07140034320648855</v>
       </c>
       <c r="C23">
-        <v>907.0481352974723</v>
+        <v>896.0240701322527</v>
       </c>
       <c r="D23">
-        <v>1135.230135297472</v>
+        <v>1135.388070132253</v>
       </c>
       <c r="E23">
-        <v>-384.478</v>
+        <v>-373.296</v>
       </c>
       <c r="F23">
-        <v>234.8219999999999</v>
+        <v>246.004</v>
       </c>
       <c r="G23">
         <v>6.64</v>
@@ -3167,28 +3167,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M23">
-        <v>12.9856566</v>
+        <v>13.6040212</v>
       </c>
       <c r="N23">
-        <v>62.69501006666667</v>
+        <v>62.07664546666667</v>
       </c>
       <c r="O23">
-        <v>7.836876258333334</v>
+        <v>7.759580683333334</v>
       </c>
       <c r="P23">
-        <v>54.85813380833333</v>
+        <v>54.31706478333334</v>
       </c>
       <c r="Q23">
-        <v>55.44413380833333</v>
+        <v>54.90306478333333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07752565423815461</v>
+        <v>0.07789114513652379</v>
       </c>
       <c r="T23">
-        <v>0.6183920520308136</v>
+        <v>0.6255161499278804</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.828020022234893</v>
+        <v>5.563110021224215</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07140034320648855</v>
+        <v>0.07139404456483497</v>
       </c>
       <c r="C24">
-        <v>896.0240701322527</v>
+        <v>885.0000489173865</v>
       </c>
       <c r="D24">
-        <v>1135.388070132253</v>
+        <v>1135.546048917386</v>
       </c>
       <c r="E24">
-        <v>-373.296</v>
+        <v>-362.114</v>
       </c>
       <c r="F24">
-        <v>246.004</v>
+        <v>257.186</v>
       </c>
       <c r="G24">
         <v>6.64</v>
@@ -3249,28 +3249,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M24">
-        <v>13.6040212</v>
+        <v>14.2223858</v>
       </c>
       <c r="N24">
-        <v>62.07664546666667</v>
+        <v>61.45828086666667</v>
       </c>
       <c r="O24">
-        <v>7.759580683333334</v>
+        <v>7.682285108333334</v>
       </c>
       <c r="P24">
-        <v>54.31706478333334</v>
+        <v>53.77599575833334</v>
       </c>
       <c r="Q24">
-        <v>54.90306478333333</v>
+        <v>54.36199575833334</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07789114513652379</v>
+        <v>0.07826612930498049</v>
       </c>
       <c r="T24">
-        <v>0.6255161499278804</v>
+        <v>0.632825289328767</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.563110021224215</v>
+        <v>5.321235672475336</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07139404456483497</v>
+        <v>0.07138774592318139</v>
       </c>
       <c r="C25">
-        <v>885.0000489173865</v>
+        <v>873.9760716712217</v>
       </c>
       <c r="D25">
-        <v>1135.546048917386</v>
+        <v>1135.704071671222</v>
       </c>
       <c r="E25">
-        <v>-362.114</v>
+        <v>-350.932</v>
       </c>
       <c r="F25">
-        <v>257.186</v>
+        <v>268.368</v>
       </c>
       <c r="G25">
         <v>6.64</v>
@@ -3331,28 +3331,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M25">
-        <v>14.2223858</v>
+        <v>14.8407504</v>
       </c>
       <c r="N25">
-        <v>61.45828086666667</v>
+        <v>60.83991626666666</v>
       </c>
       <c r="O25">
-        <v>7.682285108333334</v>
+        <v>7.604989533333333</v>
       </c>
       <c r="P25">
-        <v>53.77599575833334</v>
+        <v>53.23492673333333</v>
       </c>
       <c r="Q25">
-        <v>54.36199575833334</v>
+        <v>53.82092673333333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07826612930498049</v>
+        <v>0.07865098147787025</v>
       </c>
       <c r="T25">
-        <v>0.632825289328767</v>
+        <v>0.6403267745033613</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.321235672475336</v>
+        <v>5.09951751945553</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07138774592318139</v>
+        <v>0.07138144728152782</v>
       </c>
       <c r="C26">
-        <v>873.9760716712217</v>
+        <v>862.9521384121172</v>
       </c>
       <c r="D26">
-        <v>1135.704071671222</v>
+        <v>1135.862138412117</v>
       </c>
       <c r="E26">
-        <v>-350.932</v>
+        <v>-339.75</v>
       </c>
       <c r="F26">
-        <v>268.3679999999999</v>
+        <v>279.55</v>
       </c>
       <c r="G26">
         <v>6.64</v>
@@ -3413,28 +3413,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M26">
-        <v>14.8407504</v>
+        <v>15.459115</v>
       </c>
       <c r="N26">
-        <v>60.83991626666667</v>
+        <v>60.22155166666667</v>
       </c>
       <c r="O26">
-        <v>7.604989533333334</v>
+        <v>7.527693958333334</v>
       </c>
       <c r="P26">
-        <v>53.23492673333334</v>
+        <v>52.69385770833334</v>
       </c>
       <c r="Q26">
-        <v>53.82092673333334</v>
+        <v>53.27985770833334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07865098147787025</v>
+        <v>0.07904609637537041</v>
       </c>
       <c r="T26">
-        <v>0.6403267745033612</v>
+        <v>0.6480282992826113</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.099517519455531</v>
+        <v>4.895536818677309</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07138144728152782</v>
+        <v>0.07137514863987422</v>
       </c>
       <c r="C27">
-        <v>862.9521384121172</v>
+        <v>851.928249158442</v>
       </c>
       <c r="D27">
-        <v>1135.862138412117</v>
+        <v>1136.020249158442</v>
       </c>
       <c r="E27">
-        <v>-339.75</v>
+        <v>-328.568</v>
       </c>
       <c r="F27">
-        <v>279.55</v>
+        <v>290.732</v>
       </c>
       <c r="G27">
         <v>6.64</v>
@@ -3495,28 +3495,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M27">
-        <v>15.459115</v>
+        <v>16.0774796</v>
       </c>
       <c r="N27">
-        <v>60.22155166666667</v>
+        <v>59.60318706666666</v>
       </c>
       <c r="O27">
-        <v>7.527693958333334</v>
+        <v>7.450398383333333</v>
       </c>
       <c r="P27">
-        <v>52.69385770833334</v>
+        <v>52.15278868333333</v>
       </c>
       <c r="Q27">
-        <v>53.27985770833334</v>
+        <v>52.73878868333333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07904609637537041</v>
+        <v>0.07945189005388409</v>
       </c>
       <c r="T27">
-        <v>0.6480282992826113</v>
+        <v>0.6559379733802195</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.895536818677309</v>
+        <v>4.707246941035874</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07137514863987422</v>
+        <v>0.07136884999822064</v>
       </c>
       <c r="C28">
-        <v>851.928249158442</v>
+        <v>840.9044039285748</v>
       </c>
       <c r="D28">
-        <v>1136.020249158442</v>
+        <v>1136.178403928575</v>
       </c>
       <c r="E28">
-        <v>-328.568</v>
+        <v>-317.386</v>
       </c>
       <c r="F28">
-        <v>290.732</v>
+        <v>301.914</v>
       </c>
       <c r="G28">
         <v>6.64</v>
@@ -3577,28 +3577,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M28">
-        <v>16.0774796</v>
+        <v>16.6958442</v>
       </c>
       <c r="N28">
-        <v>59.60318706666666</v>
+        <v>58.98482246666667</v>
       </c>
       <c r="O28">
-        <v>7.450398383333333</v>
+        <v>7.373102808333334</v>
       </c>
       <c r="P28">
-        <v>52.15278868333333</v>
+        <v>51.61171965833334</v>
       </c>
       <c r="Q28">
-        <v>52.73878868333333</v>
+        <v>52.19771965833333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07945189005388409</v>
+        <v>0.07986880136742554</v>
       </c>
       <c r="T28">
-        <v>0.6559379733802195</v>
+        <v>0.6640643508777622</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.707246941035874</v>
+        <v>4.53290446173825</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07136884999822064</v>
+        <v>0.07197505135656705</v>
       </c>
       <c r="C29">
-        <v>840.9044039285748</v>
+        <v>814.70024448821</v>
       </c>
       <c r="D29">
-        <v>1136.178403928575</v>
+        <v>1121.15624448821</v>
       </c>
       <c r="E29">
-        <v>-317.386</v>
+        <v>-306.204</v>
       </c>
       <c r="F29">
-        <v>301.914</v>
+        <v>313.096</v>
       </c>
       <c r="G29">
         <v>6.64</v>
@@ -3659,45 +3659,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M29">
-        <v>16.6958442</v>
+        <v>18.0969488</v>
       </c>
       <c r="N29">
-        <v>58.98482246666667</v>
+        <v>57.58371786666667</v>
       </c>
       <c r="O29">
-        <v>7.373102808333334</v>
+        <v>7.197964733333333</v>
       </c>
       <c r="P29">
-        <v>51.61171965833334</v>
+        <v>50.38575313333333</v>
       </c>
       <c r="Q29">
-        <v>52.19771965833333</v>
+        <v>50.97175313333333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07986880136742554</v>
+        <v>0.08029729355078757</v>
       </c>
       <c r="T29">
-        <v>0.6640643508777622</v>
+        <v>0.6724164610835699</v>
       </c>
       <c r="U29">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>4.53290446173825</v>
+        <v>4.181957273740348</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07197505135656705</v>
+        <v>0.07199062771491348</v>
       </c>
       <c r="C30">
-        <v>814.70024448821</v>
+        <v>803.1374825895284</v>
       </c>
       <c r="D30">
-        <v>1121.15624448821</v>
+        <v>1120.775482589528</v>
       </c>
       <c r="E30">
-        <v>-306.204</v>
+        <v>-295.022</v>
       </c>
       <c r="F30">
-        <v>313.096</v>
+        <v>324.278</v>
       </c>
       <c r="G30">
         <v>6.64</v>
@@ -3741,28 +3741,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M30">
-        <v>18.0969488</v>
+        <v>18.7432684</v>
       </c>
       <c r="N30">
-        <v>57.58371786666667</v>
+        <v>56.93739826666667</v>
       </c>
       <c r="O30">
-        <v>7.197964733333333</v>
+        <v>7.117174783333334</v>
       </c>
       <c r="P30">
-        <v>50.38575313333333</v>
+        <v>49.82022348333334</v>
       </c>
       <c r="Q30">
-        <v>50.97175313333333</v>
+        <v>50.40622348333333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08029729355078757</v>
+        <v>0.08073785593649785</v>
       </c>
       <c r="T30">
-        <v>0.6724164610835699</v>
+        <v>0.6810038419994003</v>
       </c>
       <c r="U30">
         <v>0.0578</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.181957273740348</v>
+        <v>4.037751850507923</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07199062771491346</v>
+        <v>0.07292495407325988</v>
       </c>
       <c r="C31">
-        <v>803.1374825895288</v>
+        <v>769.579589589562</v>
       </c>
       <c r="D31">
-        <v>1120.775482589529</v>
+        <v>1098.399589589562</v>
       </c>
       <c r="E31">
-        <v>-295.022</v>
+        <v>-283.84</v>
       </c>
       <c r="F31">
-        <v>324.2779999999999</v>
+        <v>335.4599999999999</v>
       </c>
       <c r="G31">
         <v>6.64</v>
@@ -3823,45 +3823,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M31">
-        <v>18.74326839999999</v>
+        <v>20.563698</v>
       </c>
       <c r="N31">
-        <v>56.93739826666668</v>
+        <v>55.11696866666667</v>
       </c>
       <c r="O31">
-        <v>7.117174783333335</v>
+        <v>6.889621083333334</v>
       </c>
       <c r="P31">
-        <v>49.82022348333334</v>
+        <v>48.22734758333334</v>
       </c>
       <c r="Q31">
-        <v>50.40622348333334</v>
+        <v>48.81334758333334</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08073785593649785</v>
+        <v>0.0811910058189427</v>
       </c>
       <c r="T31">
-        <v>0.6810038419994002</v>
+        <v>0.689836576655683</v>
       </c>
       <c r="U31">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.037751850507924</v>
+        <v>3.680304323992051</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07292495407325988</v>
+        <v>0.07297115543160629</v>
       </c>
       <c r="C32">
-        <v>769.579589589562</v>
+        <v>757.3142871447839</v>
       </c>
       <c r="D32">
-        <v>1098.399589589562</v>
+        <v>1097.316287144784</v>
       </c>
       <c r="E32">
-        <v>-283.84</v>
+        <v>-272.658</v>
       </c>
       <c r="F32">
-        <v>335.4599999999999</v>
+        <v>346.6419999999999</v>
       </c>
       <c r="G32">
         <v>6.64</v>
@@ -3905,28 +3905,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M32">
-        <v>20.563698</v>
+        <v>21.2491546</v>
       </c>
       <c r="N32">
-        <v>55.11696866666667</v>
+        <v>54.43151206666667</v>
       </c>
       <c r="O32">
-        <v>6.889621083333334</v>
+        <v>6.803939008333334</v>
       </c>
       <c r="P32">
-        <v>48.22734758333334</v>
+        <v>47.62757305833334</v>
       </c>
       <c r="Q32">
-        <v>48.81334758333334</v>
+        <v>48.21357305833334</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0811910058189427</v>
+        <v>0.08165729048058884</v>
       </c>
       <c r="T32">
-        <v>0.689836576655683</v>
+        <v>0.6989253326063508</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.680304323992051</v>
+        <v>3.561584829669726</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07297115543160629</v>
+        <v>0.07380135678995271</v>
       </c>
       <c r="C33">
-        <v>757.3142871447839</v>
+        <v>727.0240498204242</v>
       </c>
       <c r="D33">
-        <v>1097.316287144784</v>
+        <v>1078.208049820424</v>
       </c>
       <c r="E33">
-        <v>-272.658</v>
+        <v>-261.476</v>
       </c>
       <c r="F33">
-        <v>346.6419999999999</v>
+        <v>357.824</v>
       </c>
       <c r="G33">
         <v>6.64</v>
@@ -3987,45 +3987,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M33">
-        <v>21.2491546</v>
+        <v>22.9365184</v>
       </c>
       <c r="N33">
-        <v>54.43151206666667</v>
+        <v>52.74414826666667</v>
       </c>
       <c r="O33">
-        <v>6.803939008333334</v>
+        <v>6.593018533333334</v>
       </c>
       <c r="P33">
-        <v>47.62757305833334</v>
+        <v>46.15112973333333</v>
       </c>
       <c r="Q33">
-        <v>48.21357305833334</v>
+        <v>46.73712973333333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08165729048058884</v>
+        <v>0.08213728939698929</v>
       </c>
       <c r="T33">
-        <v>0.6989253326063508</v>
+        <v>0.7082814049085088</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.561584829669726</v>
+        <v>3.299570813095447</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07380135678995271</v>
+        <v>0.07387205814829914</v>
       </c>
       <c r="C34">
-        <v>727.0240498204242</v>
+        <v>714.2454645454292</v>
       </c>
       <c r="D34">
-        <v>1078.208049820424</v>
+        <v>1076.611464545429</v>
       </c>
       <c r="E34">
-        <v>-261.476</v>
+        <v>-250.294</v>
       </c>
       <c r="F34">
-        <v>357.824</v>
+        <v>369.006</v>
       </c>
       <c r="G34">
         <v>6.64</v>
@@ -4069,28 +4069,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M34">
-        <v>22.9365184</v>
+        <v>23.6532846</v>
       </c>
       <c r="N34">
-        <v>52.74414826666667</v>
+        <v>52.02738206666667</v>
       </c>
       <c r="O34">
-        <v>6.593018533333334</v>
+        <v>6.503422758333333</v>
       </c>
       <c r="P34">
-        <v>46.15112973333333</v>
+        <v>45.52395930833333</v>
       </c>
       <c r="Q34">
-        <v>46.73712973333333</v>
+        <v>46.10995930833333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08213728939698929</v>
+        <v>0.08263161663925245</v>
       </c>
       <c r="T34">
-        <v>0.7082814049085088</v>
+        <v>0.7179167629510298</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.299570813095447</v>
+        <v>3.199583818759221</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07387205814829914</v>
+        <v>0.07394275950664556</v>
       </c>
       <c r="C35">
-        <v>714.2454645454292</v>
+        <v>701.4716006514278</v>
       </c>
       <c r="D35">
-        <v>1076.611464545429</v>
+        <v>1075.019600651428</v>
       </c>
       <c r="E35">
-        <v>-250.294</v>
+        <v>-239.112</v>
       </c>
       <c r="F35">
-        <v>369.006</v>
+        <v>380.188</v>
       </c>
       <c r="G35">
         <v>6.64</v>
@@ -4151,28 +4151,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M35">
-        <v>23.6532846</v>
+        <v>24.3700508</v>
       </c>
       <c r="N35">
-        <v>52.02738206666667</v>
+        <v>51.31061586666667</v>
       </c>
       <c r="O35">
-        <v>6.503422758333333</v>
+        <v>6.413826983333333</v>
       </c>
       <c r="P35">
-        <v>45.52395930833333</v>
+        <v>44.89678888333333</v>
       </c>
       <c r="Q35">
-        <v>46.10995930833333</v>
+        <v>45.48278888333333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08263161663925245</v>
+        <v>0.0831409234949175</v>
       </c>
       <c r="T35">
-        <v>0.7179167629510298</v>
+        <v>0.7278441015402938</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.199583818759221</v>
+        <v>3.105478412325126</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07394275950664556</v>
+        <v>0.07401346086499197</v>
       </c>
       <c r="C36">
-        <v>701.4716006514278</v>
+        <v>688.70243722642</v>
       </c>
       <c r="D36">
-        <v>1075.019600651428</v>
+        <v>1073.43243722642</v>
       </c>
       <c r="E36">
-        <v>-239.112</v>
+        <v>-227.93</v>
       </c>
       <c r="F36">
-        <v>380.188</v>
+        <v>391.3699999999999</v>
       </c>
       <c r="G36">
         <v>6.64</v>
@@ -4233,28 +4233,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M36">
-        <v>24.3700508</v>
+        <v>25.086817</v>
       </c>
       <c r="N36">
-        <v>51.31061586666667</v>
+        <v>50.59384966666667</v>
       </c>
       <c r="O36">
-        <v>6.413826983333333</v>
+        <v>6.324231208333334</v>
       </c>
       <c r="P36">
-        <v>44.89678888333333</v>
+        <v>44.26961845833334</v>
       </c>
       <c r="Q36">
-        <v>45.48278888333333</v>
+        <v>44.85561845833334</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.0831409234949175</v>
+        <v>0.08366590133075688</v>
       </c>
       <c r="T36">
-        <v>0.7278441015402938</v>
+        <v>0.7380768967015351</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.105478412325126</v>
+        <v>3.016750457687265</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07401346086499197</v>
+        <v>0.07654116222333837</v>
       </c>
       <c r="C37">
-        <v>688.70243722642</v>
+        <v>623.7010611892738</v>
       </c>
       <c r="D37">
-        <v>1073.43243722642</v>
+        <v>1019.613061189274</v>
       </c>
       <c r="E37">
-        <v>-227.93</v>
+        <v>-216.748</v>
       </c>
       <c r="F37">
-        <v>391.3699999999999</v>
+        <v>402.552</v>
       </c>
       <c r="G37">
         <v>6.64</v>
@@ -4315,45 +4315,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M37">
-        <v>25.086817</v>
+        <v>28.9434888</v>
       </c>
       <c r="N37">
-        <v>50.59384966666667</v>
+        <v>46.73717786666667</v>
       </c>
       <c r="O37">
-        <v>6.324231208333334</v>
+        <v>5.842147233333334</v>
       </c>
       <c r="P37">
-        <v>44.26961845833334</v>
+        <v>40.89503063333333</v>
       </c>
       <c r="Q37">
-        <v>44.85561845833334</v>
+        <v>41.48103063333333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08366590133075688</v>
+        <v>0.08420728472396621</v>
       </c>
       <c r="T37">
-        <v>0.7380768967015351</v>
+        <v>0.7486294667115651</v>
       </c>
       <c r="U37">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05608750000000001</v>
+        <v>0.06291250000000001</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y37">
-        <v>3.016750457687265</v>
+        <v>2.614773470801028</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07654116222333837</v>
+        <v>0.07668011358168479</v>
       </c>
       <c r="C38">
-        <v>623.7010611892738</v>
+        <v>609.7165907551312</v>
       </c>
       <c r="D38">
-        <v>1019.613061189274</v>
+        <v>1016.810590755131</v>
       </c>
       <c r="E38">
-        <v>-216.748</v>
+        <v>-205.566</v>
       </c>
       <c r="F38">
-        <v>402.5519999999999</v>
+        <v>413.7339999999999</v>
       </c>
       <c r="G38">
         <v>6.64</v>
@@ -4397,28 +4397,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M38">
-        <v>28.9434888</v>
+        <v>29.7474746</v>
       </c>
       <c r="N38">
-        <v>46.73717786666667</v>
+        <v>45.93319206666667</v>
       </c>
       <c r="O38">
-        <v>5.842147233333334</v>
+        <v>5.741649008333334</v>
       </c>
       <c r="P38">
-        <v>40.89503063333333</v>
+        <v>40.19154305833334</v>
       </c>
       <c r="Q38">
-        <v>41.48103063333333</v>
+        <v>40.77754305833334</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08420728472396621</v>
+        <v>0.08476585489156316</v>
       </c>
       <c r="T38">
-        <v>0.7486294667115651</v>
+        <v>0.7595170389441358</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.614773470801028</v>
+        <v>2.544103917536135</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07668011358168479</v>
+        <v>0.07811581494003123</v>
       </c>
       <c r="C39">
-        <v>609.7165907551312</v>
+        <v>570.4553557766661</v>
       </c>
       <c r="D39">
-        <v>1016.810590755131</v>
+        <v>988.7313557766661</v>
       </c>
       <c r="E39">
-        <v>-205.566</v>
+        <v>-194.384</v>
       </c>
       <c r="F39">
-        <v>413.7339999999999</v>
+        <v>424.9159999999999</v>
       </c>
       <c r="G39">
         <v>6.64</v>
@@ -4479,45 +4479,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M39">
-        <v>29.7474746</v>
+        <v>32.2086328</v>
       </c>
       <c r="N39">
-        <v>45.93319206666667</v>
+        <v>43.47203386666667</v>
       </c>
       <c r="O39">
-        <v>5.741649008333334</v>
+        <v>5.434004233333334</v>
       </c>
       <c r="P39">
-        <v>40.19154305833334</v>
+        <v>38.03802963333334</v>
       </c>
       <c r="Q39">
-        <v>40.77754305833334</v>
+        <v>38.62402963333334</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08476585489156316</v>
+        <v>0.08534244345166325</v>
       </c>
       <c r="T39">
-        <v>0.7595170389441358</v>
+        <v>0.7707558231842089</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.06291250000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.544103917536135</v>
+        <v>2.34970130947833</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07811581494003123</v>
+        <v>0.07828889129837764</v>
       </c>
       <c r="C40">
-        <v>570.4553557766661</v>
+        <v>555.992752057344</v>
       </c>
       <c r="D40">
-        <v>988.7313557766661</v>
+        <v>985.4507520573439</v>
       </c>
       <c r="E40">
-        <v>-194.384</v>
+        <v>-183.202</v>
       </c>
       <c r="F40">
-        <v>424.9159999999999</v>
+        <v>436.098</v>
       </c>
       <c r="G40">
         <v>6.64</v>
@@ -4561,28 +4561,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M40">
-        <v>32.2086328</v>
+        <v>33.0562284</v>
       </c>
       <c r="N40">
-        <v>43.47203386666667</v>
+        <v>42.62443826666667</v>
       </c>
       <c r="O40">
-        <v>5.434004233333334</v>
+        <v>5.328054783333333</v>
       </c>
       <c r="P40">
-        <v>38.03802963333334</v>
+        <v>37.29638348333333</v>
       </c>
       <c r="Q40">
-        <v>38.62402963333334</v>
+        <v>37.88238348333333</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08534244345166325</v>
+        <v>0.08593793655471743</v>
       </c>
       <c r="T40">
-        <v>0.7707558231842089</v>
+        <v>0.7823630921534647</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.34970130947833</v>
+        <v>2.289452557953244</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07828889129837764</v>
+        <v>0.07846196765672406</v>
       </c>
       <c r="C41">
-        <v>555.992752057344</v>
+        <v>541.5518463844219</v>
       </c>
       <c r="D41">
-        <v>985.4507520573439</v>
+        <v>982.1918463844219</v>
       </c>
       <c r="E41">
-        <v>-183.202</v>
+        <v>-172.02</v>
       </c>
       <c r="F41">
-        <v>436.098</v>
+        <v>447.28</v>
       </c>
       <c r="G41">
         <v>6.64</v>
@@ -4643,28 +4643,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M41">
-        <v>33.0562284</v>
+        <v>33.903824</v>
       </c>
       <c r="N41">
-        <v>42.62443826666667</v>
+        <v>41.77684266666667</v>
       </c>
       <c r="O41">
-        <v>5.328054783333333</v>
+        <v>5.222105333333333</v>
       </c>
       <c r="P41">
-        <v>37.29638348333333</v>
+        <v>36.55473733333334</v>
       </c>
       <c r="Q41">
-        <v>37.88238348333333</v>
+        <v>37.14073733333333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08593793655471743</v>
+        <v>0.08655327942787341</v>
       </c>
       <c r="T41">
-        <v>0.7823630921534647</v>
+        <v>0.7943572700883623</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.289452557953244</v>
+        <v>2.232216244004413</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07846196765672406</v>
+        <v>0.07863504401507047</v>
       </c>
       <c r="C42">
-        <v>541.5518463844219</v>
+        <v>527.1324241998061</v>
       </c>
       <c r="D42">
-        <v>982.1918463844219</v>
+        <v>978.954424199806</v>
       </c>
       <c r="E42">
-        <v>-172.02</v>
+        <v>-160.838</v>
       </c>
       <c r="F42">
-        <v>447.28</v>
+        <v>458.4619999999999</v>
       </c>
       <c r="G42">
         <v>6.64</v>
@@ -4725,28 +4725,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M42">
-        <v>33.903824</v>
+        <v>34.7514196</v>
       </c>
       <c r="N42">
-        <v>41.77684266666667</v>
+        <v>40.92924706666667</v>
       </c>
       <c r="O42">
-        <v>5.222105333333333</v>
+        <v>5.116155883333334</v>
       </c>
       <c r="P42">
-        <v>36.55473733333334</v>
+        <v>35.81309118333333</v>
       </c>
       <c r="Q42">
-        <v>37.14073733333333</v>
+        <v>36.39909118333333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08655327942787341</v>
+        <v>0.08718948138147536</v>
       </c>
       <c r="T42">
-        <v>0.7943572700883623</v>
+        <v>0.8067580303261378</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.232216244004413</v>
+        <v>2.177771945370159</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07863504401507047</v>
+        <v>0.07880812037341688</v>
       </c>
       <c r="C43">
-        <v>527.1324241998061</v>
+        <v>512.734273764946</v>
       </c>
       <c r="D43">
-        <v>978.954424199806</v>
+        <v>975.7382737649459</v>
       </c>
       <c r="E43">
-        <v>-160.838</v>
+        <v>-149.656</v>
       </c>
       <c r="F43">
-        <v>458.4619999999999</v>
+        <v>469.6439999999999</v>
       </c>
       <c r="G43">
         <v>6.64</v>
@@ -4807,28 +4807,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M43">
-        <v>34.7514196</v>
+        <v>35.5990152</v>
       </c>
       <c r="N43">
-        <v>40.92924706666667</v>
+        <v>40.08165146666667</v>
       </c>
       <c r="O43">
-        <v>5.116155883333334</v>
+        <v>5.010206433333334</v>
       </c>
       <c r="P43">
-        <v>35.81309118333333</v>
+        <v>35.07144503333333</v>
       </c>
       <c r="Q43">
-        <v>36.39909118333333</v>
+        <v>35.65744503333333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08718948138147536</v>
+        <v>0.08784762133347737</v>
       </c>
       <c r="T43">
-        <v>0.8067580303261378</v>
+        <v>0.8195864029859057</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.177771945370159</v>
+        <v>2.125920232385155</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07880812037341689</v>
+        <v>0.07898119673176329</v>
       </c>
       <c r="C44">
-        <v>512.7342737649458</v>
+        <v>498.3571861146709</v>
       </c>
       <c r="D44">
-        <v>975.7382737649457</v>
+        <v>972.5431861146708</v>
       </c>
       <c r="E44">
-        <v>-149.6560000000001</v>
+        <v>-138.474</v>
       </c>
       <c r="F44">
-        <v>469.6439999999999</v>
+        <v>480.8259999999999</v>
       </c>
       <c r="G44">
         <v>6.64</v>
@@ -4889,28 +4889,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M44">
-        <v>35.5990152</v>
+        <v>36.44661079999999</v>
       </c>
       <c r="N44">
-        <v>40.08165146666667</v>
+        <v>39.23405586666667</v>
       </c>
       <c r="O44">
-        <v>5.010206433333334</v>
+        <v>4.904256983333334</v>
       </c>
       <c r="P44">
-        <v>35.07144503333333</v>
+        <v>34.32979888333334</v>
       </c>
       <c r="Q44">
-        <v>35.65744503333333</v>
+        <v>34.91579888333334</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08784762133347737</v>
+        <v>0.08852885391537418</v>
       </c>
       <c r="T44">
-        <v>0.8195864029859056</v>
+        <v>0.8328648939846125</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.125920232385155</v>
+        <v>2.076480226980849</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07898119673176329</v>
+        <v>0.07915427309010972</v>
       </c>
       <c r="C45">
-        <v>498.3571861146709</v>
+        <v>484.0009550119302</v>
       </c>
       <c r="D45">
-        <v>972.5431861146708</v>
+        <v>969.3689550119301</v>
       </c>
       <c r="E45">
-        <v>-138.474</v>
+        <v>-127.292</v>
       </c>
       <c r="F45">
-        <v>480.8259999999999</v>
+        <v>492.0079999999999</v>
       </c>
       <c r="G45">
         <v>6.64</v>
@@ -4971,28 +4971,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M45">
-        <v>36.44661079999999</v>
+        <v>37.2942064</v>
       </c>
       <c r="N45">
-        <v>39.23405586666667</v>
+        <v>38.38646026666667</v>
       </c>
       <c r="O45">
-        <v>4.904256983333334</v>
+        <v>4.798307533333333</v>
       </c>
       <c r="P45">
-        <v>34.32979888333334</v>
+        <v>33.58815273333333</v>
       </c>
       <c r="Q45">
-        <v>34.91579888333334</v>
+        <v>34.17415273333333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08852885391537418</v>
+        <v>0.08923441623233877</v>
       </c>
       <c r="T45">
-        <v>0.8328648939846125</v>
+        <v>0.8466176168047019</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.076480226980849</v>
+        <v>2.029287494549466</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07915427309010972</v>
+        <v>0.08491859944845613</v>
       </c>
       <c r="C46">
-        <v>484.0009550119302</v>
+        <v>377.7771996190778</v>
       </c>
       <c r="D46">
-        <v>969.3689550119301</v>
+        <v>874.3271996190778</v>
       </c>
       <c r="E46">
-        <v>-127.292</v>
+        <v>-116.11</v>
       </c>
       <c r="F46">
-        <v>492.0079999999999</v>
+        <v>503.1899999999999</v>
       </c>
       <c r="G46">
         <v>6.64</v>
@@ -5053,45 +5053,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M46">
-        <v>37.2942064</v>
+        <v>45.2871</v>
       </c>
       <c r="N46">
-        <v>38.38646026666667</v>
+        <v>30.39356666666667</v>
       </c>
       <c r="O46">
-        <v>4.798307533333333</v>
+        <v>3.799195833333334</v>
       </c>
       <c r="P46">
-        <v>33.58815273333333</v>
+        <v>26.59437083333334</v>
       </c>
       <c r="Q46">
-        <v>34.17415273333333</v>
+        <v>27.18037083333333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08923441623233877</v>
+        <v>0.08996563536082931</v>
       </c>
       <c r="T46">
-        <v>0.8466176168047019</v>
+        <v>0.8608704386364309</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.06632500000000001</v>
+        <v>0.07875</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.029287494549466</v>
+        <v>1.671130778227501</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08491859944845613</v>
+        <v>0.08521592580680254</v>
       </c>
       <c r="C47">
-        <v>377.7771996190778</v>
+        <v>362.1958001078444</v>
       </c>
       <c r="D47">
-        <v>874.3271996190778</v>
+        <v>869.9278001078444</v>
       </c>
       <c r="E47">
-        <v>-116.11</v>
+        <v>-104.928</v>
       </c>
       <c r="F47">
-        <v>503.1899999999999</v>
+        <v>514.372</v>
       </c>
       <c r="G47">
         <v>6.64</v>
@@ -5135,28 +5135,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M47">
-        <v>45.2871</v>
+        <v>46.29348</v>
       </c>
       <c r="N47">
-        <v>30.39356666666667</v>
+        <v>29.38718666666667</v>
       </c>
       <c r="O47">
-        <v>3.799195833333334</v>
+        <v>3.673398333333334</v>
       </c>
       <c r="P47">
-        <v>26.59437083333334</v>
+        <v>25.71378833333334</v>
       </c>
       <c r="Q47">
-        <v>27.18037083333333</v>
+        <v>26.29978833333334</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08996563536082931</v>
+        <v>0.09072393667926396</v>
       </c>
       <c r="T47">
-        <v>0.8608704386364309</v>
+        <v>0.8756511427582239</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.671130778227501</v>
+        <v>1.634801848266034</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08521592580680254</v>
+        <v>0.08551325216514896</v>
       </c>
       <c r="C48">
-        <v>362.1958001078444</v>
+        <v>346.6584523325628</v>
       </c>
       <c r="D48">
-        <v>869.9278001078444</v>
+        <v>865.5724523325628</v>
       </c>
       <c r="E48">
-        <v>-104.928</v>
+        <v>-93.74599999999998</v>
       </c>
       <c r="F48">
-        <v>514.372</v>
+        <v>525.554</v>
       </c>
       <c r="G48">
         <v>6.64</v>
@@ -5217,28 +5217,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M48">
-        <v>46.29348</v>
+        <v>47.29986</v>
       </c>
       <c r="N48">
-        <v>29.38718666666667</v>
+        <v>28.38080666666667</v>
       </c>
       <c r="O48">
-        <v>3.673398333333334</v>
+        <v>3.547600833333334</v>
       </c>
       <c r="P48">
-        <v>25.71378833333334</v>
+        <v>24.83320583333334</v>
       </c>
       <c r="Q48">
-        <v>26.29978833333334</v>
+        <v>25.41920583333334</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09072393667926396</v>
+        <v>0.09151085314179047</v>
       </c>
       <c r="T48">
-        <v>0.8756511427582239</v>
+        <v>0.8909896092997073</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.634801848266034</v>
+        <v>1.60001883021782</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08551325216514896</v>
+        <v>0.08581057852349537</v>
       </c>
       <c r="C49">
-        <v>346.6584523325628</v>
+        <v>331.1644979460012</v>
       </c>
       <c r="D49">
-        <v>865.5724523325628</v>
+        <v>861.2604979460012</v>
       </c>
       <c r="E49">
-        <v>-93.74599999999998</v>
+        <v>-82.56399999999996</v>
       </c>
       <c r="F49">
-        <v>525.554</v>
+        <v>536.736</v>
       </c>
       <c r="G49">
         <v>6.64</v>
@@ -5299,28 +5299,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M49">
-        <v>47.29986</v>
+        <v>48.30624</v>
       </c>
       <c r="N49">
-        <v>28.38080666666667</v>
+        <v>27.37442666666667</v>
       </c>
       <c r="O49">
-        <v>3.547600833333334</v>
+        <v>3.421803333333334</v>
       </c>
       <c r="P49">
-        <v>24.83320583333334</v>
+        <v>23.95262333333334</v>
       </c>
       <c r="Q49">
-        <v>25.41920583333334</v>
+        <v>24.53862333333334</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09151085314179047</v>
+        <v>0.09232803562210648</v>
       </c>
       <c r="T49">
-        <v>0.8909896092997073</v>
+        <v>0.9069180168620169</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.60001883021782</v>
+        <v>1.566685104588283</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08581057852349537</v>
+        <v>0.08610790488184178</v>
       </c>
       <c r="C50">
-        <v>331.1644979460013</v>
+        <v>315.7132916544467</v>
       </c>
       <c r="D50">
-        <v>861.2604979460012</v>
+        <v>856.9912916544466</v>
       </c>
       <c r="E50">
-        <v>-82.56400000000008</v>
+        <v>-71.38200000000006</v>
       </c>
       <c r="F50">
-        <v>536.7359999999999</v>
+        <v>547.9179999999999</v>
       </c>
       <c r="G50">
         <v>6.64</v>
@@ -5381,28 +5381,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M50">
-        <v>48.30623999999999</v>
+        <v>49.31261999999999</v>
       </c>
       <c r="N50">
-        <v>27.37442666666668</v>
+        <v>26.36804666666668</v>
       </c>
       <c r="O50">
-        <v>3.421803333333335</v>
+        <v>3.296005833333335</v>
       </c>
       <c r="P50">
-        <v>23.95262333333334</v>
+        <v>23.07204083333334</v>
       </c>
       <c r="Q50">
-        <v>24.53862333333334</v>
+        <v>23.65804083333334</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09232803562210648</v>
+        <v>0.09317726447419958</v>
       </c>
       <c r="T50">
-        <v>0.9069180168620168</v>
+        <v>0.9234710678581425</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.566685104588283</v>
+        <v>1.534711939188522</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08610790488184178</v>
+        <v>0.0864052312401882</v>
       </c>
       <c r="C51">
-        <v>315.7132916544467</v>
+        <v>300.3042008957746</v>
       </c>
       <c r="D51">
-        <v>856.9912916544466</v>
+        <v>852.7642008957745</v>
       </c>
       <c r="E51">
-        <v>-71.38200000000006</v>
+        <v>-60.20000000000005</v>
       </c>
       <c r="F51">
-        <v>547.9179999999999</v>
+        <v>559.0999999999999</v>
       </c>
       <c r="G51">
         <v>6.64</v>
@@ -5463,28 +5463,28 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M51">
-        <v>49.31261999999999</v>
+        <v>50.31899999999999</v>
       </c>
       <c r="N51">
-        <v>26.36804666666668</v>
+        <v>25.36166666666668</v>
       </c>
       <c r="O51">
-        <v>3.296005833333335</v>
+        <v>3.170208333333335</v>
       </c>
       <c r="P51">
-        <v>23.07204083333334</v>
+        <v>22.19145833333334</v>
       </c>
       <c r="Q51">
-        <v>23.65804083333334</v>
+        <v>22.77745833333334</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09317726447419958</v>
+        <v>0.0940604624803764</v>
       </c>
       <c r="T51">
-        <v>0.9234710678581425</v>
+        <v>0.9406862408941132</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.534711939188522</v>
+        <v>1.504017700404751</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.0864052312401882</v>
+        <v>0.1131054774542718</v>
       </c>
       <c r="C52">
-        <v>300.3042008957746</v>
+        <v>27.34787130979998</v>
       </c>
       <c r="D52">
-        <v>852.7642008957745</v>
+        <v>590.9898713097999</v>
       </c>
       <c r="E52">
-        <v>-60.20000000000005</v>
+        <v>-49.01800000000003</v>
       </c>
       <c r="F52">
-        <v>559.0999999999999</v>
+        <v>570.2819999999999</v>
       </c>
       <c r="G52">
         <v>6.64</v>
@@ -5545,45 +5545,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M52">
-        <v>50.31899999999999</v>
+        <v>83.7173976</v>
       </c>
       <c r="N52">
-        <v>25.36166666666668</v>
+        <v>-8.036730933333331</v>
       </c>
       <c r="O52">
-        <v>3.170208333333335</v>
+        <v>-1.004591366666666</v>
       </c>
       <c r="P52">
-        <v>22.19145833333334</v>
+        <v>-7.032139566666665</v>
       </c>
       <c r="Q52">
-        <v>22.77745833333334</v>
+        <v>-6.446139566666664</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.0940604624803764</v>
+        <v>0.0953011775898949</v>
       </c>
       <c r="T52">
-        <v>0.9406862408941132</v>
+        <v>0.9648700877204478</v>
       </c>
       <c r="U52">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.125</v>
+        <v>0.1130002078962537</v>
       </c>
       <c r="W52">
-        <v>0.07875</v>
+        <v>0.13021156948083</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y52">
-        <v>1.504017700404751</v>
+        <v>0.9040016631700298</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1131054774542718</v>
+        <v>0.1141154774542718</v>
       </c>
       <c r="C53">
-        <v>27.34787130979998</v>
+        <v>9.382114023735085</v>
       </c>
       <c r="D53">
-        <v>590.9898713097999</v>
+        <v>584.206114023735</v>
       </c>
       <c r="E53">
-        <v>-49.01800000000003</v>
+        <v>-37.83600000000001</v>
       </c>
       <c r="F53">
-        <v>570.2819999999999</v>
+        <v>581.4639999999999</v>
       </c>
       <c r="G53">
         <v>6.64</v>
@@ -5627,37 +5627,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M53">
-        <v>83.7173976</v>
+        <v>85.3589152</v>
       </c>
       <c r="N53">
-        <v>-8.036730933333331</v>
+        <v>-9.678248533333331</v>
       </c>
       <c r="O53">
-        <v>-1.004591366666666</v>
+        <v>-1.209781066666666</v>
       </c>
       <c r="P53">
-        <v>-7.032139566666665</v>
+        <v>-8.468467466666665</v>
       </c>
       <c r="Q53">
-        <v>-6.446139566666664</v>
+        <v>-7.882467466666665</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0953011775898949</v>
+        <v>0.09633245212301772</v>
       </c>
       <c r="T53">
-        <v>0.9648700877204478</v>
+        <v>0.9849715478812905</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.1130002078962537</v>
+        <v>0.1108271269751719</v>
       </c>
       <c r="W53">
-        <v>0.13021156948083</v>
+        <v>0.1305305777600448</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9040016631700298</v>
+        <v>0.8866170158013755</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1141154774542718</v>
+        <v>0.1151254774542718</v>
       </c>
       <c r="C54">
-        <v>9.382114023735085</v>
+        <v>-8.429674064911978</v>
       </c>
       <c r="D54">
-        <v>584.206114023735</v>
+        <v>577.576325935088</v>
       </c>
       <c r="E54">
-        <v>-37.83600000000001</v>
+        <v>-26.654</v>
       </c>
       <c r="F54">
-        <v>581.4639999999999</v>
+        <v>592.646</v>
       </c>
       <c r="G54">
         <v>6.64</v>
@@ -5709,37 +5709,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M54">
-        <v>85.3589152</v>
+        <v>87.0004328</v>
       </c>
       <c r="N54">
-        <v>-9.678248533333331</v>
+        <v>-11.31976613333333</v>
       </c>
       <c r="O54">
-        <v>-1.209781066666666</v>
+        <v>-1.414970766666666</v>
       </c>
       <c r="P54">
-        <v>-8.468467466666665</v>
+        <v>-9.904795366666665</v>
       </c>
       <c r="Q54">
-        <v>-7.882467466666665</v>
+        <v>-9.318795366666665</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09633245212301772</v>
+        <v>0.09740761067882661</v>
       </c>
       <c r="T54">
-        <v>0.9849715478812905</v>
+        <v>1.005928389325573</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1108271269751719</v>
+        <v>0.1087360491077159</v>
       </c>
       <c r="W54">
-        <v>0.1305305777600448</v>
+        <v>0.1308375479909873</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8866170158013755</v>
+        <v>0.8698883928617269</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1151254774542718</v>
+        <v>0.1161354774542718</v>
       </c>
       <c r="C55">
-        <v>-8.429674064911978</v>
+        <v>-26.09267603564274</v>
       </c>
       <c r="D55">
-        <v>577.576325935088</v>
+        <v>571.0953239643572</v>
       </c>
       <c r="E55">
-        <v>-26.654</v>
+        <v>-15.47199999999998</v>
       </c>
       <c r="F55">
-        <v>592.646</v>
+        <v>603.828</v>
       </c>
       <c r="G55">
         <v>6.64</v>
@@ -5791,37 +5791,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M55">
-        <v>87.0004328</v>
+        <v>88.6419504</v>
       </c>
       <c r="N55">
-        <v>-11.31976613333333</v>
+        <v>-12.96128373333333</v>
       </c>
       <c r="O55">
-        <v>-1.414970766666666</v>
+        <v>-1.620160466666666</v>
       </c>
       <c r="P55">
-        <v>-9.904795366666665</v>
+        <v>-11.34112326666667</v>
       </c>
       <c r="Q55">
-        <v>-9.318795366666665</v>
+        <v>-10.75512326666666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09740761067882661</v>
+        <v>0.0985295152588011</v>
       </c>
       <c r="T55">
-        <v>1.005928389325573</v>
+        <v>1.027796397789173</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1087360491077159</v>
+        <v>0.1067224185686841</v>
       </c>
       <c r="W55">
-        <v>0.1308375479909873</v>
+        <v>0.1311331489541172</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8698883928617269</v>
+        <v>0.8537793485494727</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1161354774542718</v>
+        <v>0.1171454774542718</v>
       </c>
       <c r="C56">
-        <v>-26.09267603564274</v>
+        <v>-43.61184491144377</v>
       </c>
       <c r="D56">
-        <v>571.0953239643572</v>
+        <v>564.7581550885562</v>
       </c>
       <c r="E56">
-        <v>-15.47199999999998</v>
+        <v>-4.289999999999964</v>
       </c>
       <c r="F56">
-        <v>603.828</v>
+        <v>615.01</v>
       </c>
       <c r="G56">
         <v>6.64</v>
@@ -5873,37 +5873,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M56">
-        <v>88.6419504</v>
+        <v>90.28346800000001</v>
       </c>
       <c r="N56">
-        <v>-12.96128373333333</v>
+        <v>-14.60280133333335</v>
       </c>
       <c r="O56">
-        <v>-1.620160466666666</v>
+        <v>-1.825350166666668</v>
       </c>
       <c r="P56">
-        <v>-11.34112326666667</v>
+        <v>-12.77745116666668</v>
       </c>
       <c r="Q56">
-        <v>-10.75512326666666</v>
+        <v>-12.19145116666668</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.0985295152588011</v>
+        <v>0.09970128226455222</v>
       </c>
       <c r="T56">
-        <v>1.027796397789173</v>
+        <v>1.050636317740043</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1067224185686841</v>
+        <v>0.1047820109583444</v>
       </c>
       <c r="W56">
-        <v>0.1311331489541172</v>
+        <v>0.131418000791315</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8537793485494727</v>
+        <v>0.8382560876667549</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1171454774542718</v>
+        <v>0.1181554774542718</v>
       </c>
       <c r="C57">
-        <v>-43.61184491144377</v>
+        <v>-60.99191628283211</v>
       </c>
       <c r="D57">
-        <v>564.7581550885562</v>
+        <v>558.5600837171679</v>
       </c>
       <c r="E57">
-        <v>-4.289999999999964</v>
+        <v>6.892000000000053</v>
       </c>
       <c r="F57">
-        <v>615.01</v>
+        <v>626.192</v>
       </c>
       <c r="G57">
         <v>6.64</v>
@@ -5955,37 +5955,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M57">
-        <v>90.28346800000001</v>
+        <v>91.92498560000001</v>
       </c>
       <c r="N57">
-        <v>-14.60280133333335</v>
+        <v>-16.24431893333335</v>
       </c>
       <c r="O57">
-        <v>-1.825350166666668</v>
+        <v>-2.030539866666668</v>
       </c>
       <c r="P57">
-        <v>-12.77745116666668</v>
+        <v>-14.21377906666668</v>
       </c>
       <c r="Q57">
-        <v>-12.19145116666668</v>
+        <v>-13.62777906666668</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09970128226455222</v>
+        <v>0.1009263114069284</v>
       </c>
       <c r="T57">
-        <v>1.050636317740043</v>
+        <v>1.074514415870499</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1047820109583444</v>
+        <v>0.1029109036198025</v>
       </c>
       <c r="W57">
-        <v>0.131418000791315</v>
+        <v>0.131692679348613</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8382560876667549</v>
+        <v>0.8232872289584199</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1181554774542718</v>
+        <v>0.1191654774542718</v>
       </c>
       <c r="C58">
-        <v>-60.99191628283211</v>
+        <v>-78.23742010965361</v>
       </c>
       <c r="D58">
-        <v>558.5600837171679</v>
+        <v>552.4965798903463</v>
       </c>
       <c r="E58">
-        <v>6.892000000000053</v>
+        <v>18.07399999999996</v>
       </c>
       <c r="F58">
-        <v>626.192</v>
+        <v>637.3739999999999</v>
       </c>
       <c r="G58">
         <v>6.64</v>
@@ -6037,37 +6037,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M58">
-        <v>91.92498560000001</v>
+        <v>93.5665032</v>
       </c>
       <c r="N58">
-        <v>-16.24431893333335</v>
+        <v>-17.88583653333333</v>
       </c>
       <c r="O58">
-        <v>-2.030539866666668</v>
+        <v>-2.235729566666667</v>
       </c>
       <c r="P58">
-        <v>-14.21377906666668</v>
+        <v>-15.65010696666667</v>
       </c>
       <c r="Q58">
-        <v>-13.62777906666668</v>
+        <v>-15.06410696666667</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1009263114069284</v>
+        <v>0.10220831864895</v>
       </c>
       <c r="T58">
-        <v>1.074514415870499</v>
+        <v>1.099503123216324</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1029109036198025</v>
+        <v>0.1011054491703323</v>
       </c>
       <c r="W58">
-        <v>0.131692679348613</v>
+        <v>0.1319577200617952</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8232872289584199</v>
+        <v>0.8088435933626583</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1191654774542718</v>
+        <v>0.1518943826355777</v>
       </c>
       <c r="C59">
-        <v>-78.23742010965361</v>
+        <v>-233.1963930006399</v>
       </c>
       <c r="D59">
-        <v>552.4965798903463</v>
+        <v>408.71960699936</v>
       </c>
       <c r="E59">
-        <v>18.07399999999996</v>
+        <v>29.25599999999997</v>
       </c>
       <c r="F59">
-        <v>637.3739999999999</v>
+        <v>648.5559999999999</v>
       </c>
       <c r="G59">
         <v>6.64</v>
@@ -6119,45 +6119,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M59">
-        <v>93.5665032</v>
+        <v>130.2300448</v>
       </c>
       <c r="N59">
-        <v>-17.88583653333333</v>
+        <v>-54.54937813333333</v>
       </c>
       <c r="O59">
-        <v>-2.235729566666667</v>
+        <v>-6.818672266666667</v>
       </c>
       <c r="P59">
-        <v>-15.65010696666667</v>
+        <v>-47.73070586666667</v>
       </c>
       <c r="Q59">
-        <v>-15.06410696666667</v>
+        <v>-47.14470586666667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.10220831864895</v>
+        <v>0.1045011480960819</v>
       </c>
       <c r="T59">
-        <v>1.099503123216324</v>
+        <v>1.14419463678213</v>
       </c>
       <c r="U59">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1011054491703323</v>
+        <v>0.07264132748983999</v>
       </c>
       <c r="W59">
-        <v>0.1319577200617952</v>
+        <v>0.1862136214400401</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.8088435933626583</v>
+        <v>0.5811306199187198</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1518943826355776</v>
+        <v>0.1534443826355777</v>
       </c>
       <c r="C60">
-        <v>-233.1963930006397</v>
+        <v>-249.3542260479993</v>
       </c>
       <c r="D60">
-        <v>408.7196069993601</v>
+        <v>403.7437739520005</v>
       </c>
       <c r="E60">
-        <v>29.25599999999986</v>
+        <v>40.43799999999987</v>
       </c>
       <c r="F60">
-        <v>648.5559999999998</v>
+        <v>659.7379999999998</v>
       </c>
       <c r="G60">
         <v>6.64</v>
@@ -6201,37 +6201,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M60">
-        <v>130.2300448</v>
+        <v>132.4753904</v>
       </c>
       <c r="N60">
-        <v>-54.54937813333331</v>
+        <v>-56.79472373333331</v>
       </c>
       <c r="O60">
-        <v>-6.818672266666663</v>
+        <v>-7.099340466666664</v>
       </c>
       <c r="P60">
-        <v>-47.73070586666664</v>
+        <v>-49.69538326666665</v>
       </c>
       <c r="Q60">
-        <v>-47.14470586666664</v>
+        <v>-49.10938326666665</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1045011480960819</v>
+        <v>0.1059328834154985</v>
       </c>
       <c r="T60">
-        <v>1.14419463678213</v>
+        <v>1.172101823045109</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.07264132748984001</v>
+        <v>0.07141011854933424</v>
       </c>
       <c r="W60">
-        <v>0.1862136214400401</v>
+        <v>0.1864608481952937</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5811306199187201</v>
+        <v>0.5712809483946739</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1534443826355777</v>
+        <v>0.1549943826355777</v>
       </c>
       <c r="C61">
-        <v>-249.3542260479993</v>
+        <v>-265.3923627578192</v>
       </c>
       <c r="D61">
-        <v>403.7437739520005</v>
+        <v>398.8876372421806</v>
       </c>
       <c r="E61">
-        <v>40.43799999999987</v>
+        <v>51.61999999999989</v>
       </c>
       <c r="F61">
-        <v>659.7379999999998</v>
+        <v>670.9199999999998</v>
       </c>
       <c r="G61">
         <v>6.64</v>
@@ -6283,37 +6283,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M61">
-        <v>132.4753904</v>
+        <v>134.720736</v>
       </c>
       <c r="N61">
-        <v>-56.79472373333331</v>
+        <v>-59.04006933333329</v>
       </c>
       <c r="O61">
-        <v>-7.099340466666664</v>
+        <v>-7.380008666666662</v>
       </c>
       <c r="P61">
-        <v>-49.69538326666665</v>
+        <v>-51.66006066666663</v>
       </c>
       <c r="Q61">
-        <v>-49.10938326666665</v>
+        <v>-51.07406066666663</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1059328834154985</v>
+        <v>0.107436205500886</v>
       </c>
       <c r="T61">
-        <v>1.172101823045109</v>
+        <v>1.201404368621236</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.07141011854933424</v>
+        <v>0.07021994990684534</v>
       </c>
       <c r="W61">
-        <v>0.1864608481952937</v>
+        <v>0.1866998340587055</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5712809483946739</v>
+        <v>0.5617595992547628</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1549943826355777</v>
+        <v>0.1565443826355777</v>
       </c>
       <c r="C62">
-        <v>-265.3923627578192</v>
+        <v>-281.3150708386595</v>
       </c>
       <c r="D62">
-        <v>398.8876372421806</v>
+        <v>394.1469291613404</v>
       </c>
       <c r="E62">
-        <v>51.61999999999989</v>
+        <v>62.80199999999991</v>
       </c>
       <c r="F62">
-        <v>670.9199999999998</v>
+        <v>682.1019999999999</v>
       </c>
       <c r="G62">
         <v>6.64</v>
@@ -6365,37 +6365,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M62">
-        <v>134.720736</v>
+        <v>136.9660816</v>
       </c>
       <c r="N62">
-        <v>-59.04006933333329</v>
+        <v>-61.2854149333333</v>
       </c>
       <c r="O62">
-        <v>-7.380008666666662</v>
+        <v>-7.660676866666662</v>
       </c>
       <c r="P62">
-        <v>-51.66006066666663</v>
+        <v>-53.62473806666664</v>
       </c>
       <c r="Q62">
-        <v>-51.07406066666663</v>
+        <v>-53.03873806666664</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.107436205500886</v>
+        <v>0.1090166210265497</v>
       </c>
       <c r="T62">
-        <v>1.201404368621236</v>
+        <v>1.232209608842294</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.07021994990684534</v>
+        <v>0.06906880318706099</v>
       </c>
       <c r="W62">
-        <v>0.1866998340587055</v>
+        <v>0.1869309843200382</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5617595992547628</v>
+        <v>0.5525504254964879</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1565443826355777</v>
+        <v>0.1580943826355777</v>
       </c>
       <c r="C63">
-        <v>-281.3150708386595</v>
+        <v>-297.1264174981914</v>
       </c>
       <c r="D63">
-        <v>394.1469291613404</v>
+        <v>389.5175825018085</v>
       </c>
       <c r="E63">
-        <v>62.80199999999991</v>
+        <v>73.98399999999992</v>
       </c>
       <c r="F63">
-        <v>682.1019999999999</v>
+        <v>693.2839999999999</v>
       </c>
       <c r="G63">
         <v>6.64</v>
@@ -6447,37 +6447,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M63">
-        <v>136.9660816</v>
+        <v>139.2114272</v>
       </c>
       <c r="N63">
-        <v>-61.2854149333333</v>
+        <v>-63.53076053333331</v>
       </c>
       <c r="O63">
-        <v>-7.660676866666662</v>
+        <v>-7.941345066666663</v>
       </c>
       <c r="P63">
-        <v>-53.62473806666664</v>
+        <v>-55.58941546666664</v>
       </c>
       <c r="Q63">
-        <v>-53.03873806666664</v>
+        <v>-55.00341546666665</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1090166210265497</v>
+        <v>0.1106802163167221</v>
       </c>
       <c r="T63">
-        <v>1.232209608842294</v>
+        <v>1.264636177496038</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.06906880318706099</v>
+        <v>0.06795479023243096</v>
       </c>
       <c r="W63">
-        <v>0.1869309843200382</v>
+        <v>0.1871546781213279</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5525504254964879</v>
+        <v>0.5436383218594478</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1580943826355777</v>
+        <v>0.1596443826355776</v>
       </c>
       <c r="C64">
-        <v>-297.1264174981914</v>
+        <v>-312.8302810811537</v>
       </c>
       <c r="D64">
-        <v>389.5175825018085</v>
+        <v>384.9957189188463</v>
       </c>
       <c r="E64">
-        <v>73.98399999999992</v>
+        <v>85.16599999999994</v>
       </c>
       <c r="F64">
-        <v>693.2839999999999</v>
+        <v>704.4659999999999</v>
       </c>
       <c r="G64">
         <v>6.64</v>
@@ -6529,37 +6529,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M64">
-        <v>139.2114272</v>
+        <v>141.4567728</v>
       </c>
       <c r="N64">
-        <v>-63.53076053333331</v>
+        <v>-65.77610613333331</v>
       </c>
       <c r="O64">
-        <v>-7.941345066666663</v>
+        <v>-8.222013266666664</v>
       </c>
       <c r="P64">
-        <v>-55.58941546666664</v>
+        <v>-57.55409286666665</v>
       </c>
       <c r="Q64">
-        <v>-55.00341546666665</v>
+        <v>-56.96809286666665</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1106802163167221</v>
+        <v>0.1124337356766335</v>
       </c>
       <c r="T64">
-        <v>1.264636177496038</v>
+        <v>1.29881553364458</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.06795479023243096</v>
+        <v>0.06687614276842413</v>
       </c>
       <c r="W64">
-        <v>0.1871546781213279</v>
+        <v>0.1873712705321005</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5436383218594478</v>
+        <v>0.535009142147393</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1596443826355776</v>
+        <v>0.1611943826355777</v>
       </c>
       <c r="C65">
-        <v>-312.8302810811537</v>
+        <v>-328.4303619059881</v>
       </c>
       <c r="D65">
-        <v>384.9957189188463</v>
+        <v>380.5776380940118</v>
       </c>
       <c r="E65">
-        <v>85.16599999999994</v>
+        <v>96.34799999999996</v>
       </c>
       <c r="F65">
-        <v>704.4659999999999</v>
+        <v>715.6479999999999</v>
       </c>
       <c r="G65">
         <v>6.64</v>
@@ -6611,37 +6611,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M65">
-        <v>141.4567728</v>
+        <v>143.7021184</v>
       </c>
       <c r="N65">
-        <v>-65.77610613333331</v>
+        <v>-68.02145173333332</v>
       </c>
       <c r="O65">
-        <v>-8.222013266666664</v>
+        <v>-8.502681466666665</v>
       </c>
       <c r="P65">
-        <v>-57.55409286666665</v>
+        <v>-59.51877026666666</v>
       </c>
       <c r="Q65">
-        <v>-56.96809286666665</v>
+        <v>-58.93277026666666</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1124337356766335</v>
+        <v>0.1142846727787622</v>
       </c>
       <c r="T65">
-        <v>1.29881553364458</v>
+        <v>1.334893742912485</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.06687614276842413</v>
+        <v>0.0658312030376675</v>
       </c>
       <c r="W65">
-        <v>0.1873712705321005</v>
+        <v>0.1875810944300364</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.535009142147393</v>
+        <v>0.52664962430134</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1611943826355777</v>
+        <v>0.1627443826355777</v>
       </c>
       <c r="C66">
-        <v>-328.4303619059881</v>
+        <v>-343.9301923637959</v>
       </c>
       <c r="D66">
-        <v>380.5776380940118</v>
+        <v>376.2598076362041</v>
       </c>
       <c r="E66">
-        <v>96.34799999999996</v>
+        <v>107.53</v>
       </c>
       <c r="F66">
-        <v>715.6479999999999</v>
+        <v>726.8299999999999</v>
       </c>
       <c r="G66">
         <v>6.64</v>
@@ -6693,37 +6693,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M66">
-        <v>143.7021184</v>
+        <v>145.947464</v>
       </c>
       <c r="N66">
-        <v>-68.02145173333332</v>
+        <v>-70.26679733333333</v>
       </c>
       <c r="O66">
-        <v>-8.502681466666665</v>
+        <v>-8.783349666666666</v>
       </c>
       <c r="P66">
-        <v>-59.51877026666666</v>
+        <v>-61.48344766666666</v>
       </c>
       <c r="Q66">
-        <v>-58.93277026666666</v>
+        <v>-60.89744766666666</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1142846727787622</v>
+        <v>0.1162413777152982</v>
       </c>
       <c r="T66">
-        <v>1.334893742912485</v>
+        <v>1.373033564138556</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.0658312030376675</v>
+        <v>0.06481841529862645</v>
       </c>
       <c r="W66">
-        <v>0.1875810944300364</v>
+        <v>0.1877844622080358</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.52664962430134</v>
+        <v>0.5185473223890116</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1627443826355777</v>
+        <v>0.1642943826355777</v>
       </c>
       <c r="C67">
-        <v>-343.9301923637959</v>
+        <v>-359.3331463375415</v>
       </c>
       <c r="D67">
-        <v>376.2598076362041</v>
+        <v>372.0388536624585</v>
       </c>
       <c r="E67">
-        <v>107.53</v>
+        <v>118.712</v>
       </c>
       <c r="F67">
-        <v>726.8299999999999</v>
+        <v>738.0119999999999</v>
       </c>
       <c r="G67">
         <v>6.64</v>
@@ -6775,37 +6775,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M67">
-        <v>145.947464</v>
+        <v>148.1928096</v>
       </c>
       <c r="N67">
-        <v>-70.26679733333333</v>
+        <v>-72.51214293333334</v>
       </c>
       <c r="O67">
-        <v>-8.783349666666666</v>
+        <v>-9.064017866666667</v>
       </c>
       <c r="P67">
-        <v>-61.48344766666666</v>
+        <v>-63.44812506666667</v>
       </c>
       <c r="Q67">
-        <v>-60.89744766666666</v>
+        <v>-62.86212506666667</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1162413777152982</v>
+        <v>0.1183131829422188</v>
       </c>
       <c r="T67">
-        <v>1.373033564138556</v>
+        <v>1.413416904260278</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.06481841529862645</v>
+        <v>0.06383631809713211</v>
       </c>
       <c r="W67">
-        <v>0.1877844622080358</v>
+        <v>0.1879816673260959</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5185473223890116</v>
+        <v>0.5106905447770569</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1642943826355777</v>
+        <v>0.1658443826355777</v>
       </c>
       <c r="C68">
-        <v>-359.3331463375415</v>
+        <v>-374.6424479942917</v>
       </c>
       <c r="D68">
-        <v>372.0388536624585</v>
+        <v>367.9115520057082</v>
       </c>
       <c r="E68">
-        <v>118.712</v>
+        <v>129.894</v>
       </c>
       <c r="F68">
-        <v>738.0119999999999</v>
+        <v>749.194</v>
       </c>
       <c r="G68">
         <v>6.64</v>
@@ -6857,37 +6857,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M68">
-        <v>148.1928096</v>
+        <v>150.4381552</v>
       </c>
       <c r="N68">
-        <v>-72.51214293333334</v>
+        <v>-74.75748853333332</v>
       </c>
       <c r="O68">
-        <v>-9.064017866666667</v>
+        <v>-9.344686066666664</v>
       </c>
       <c r="P68">
-        <v>-63.44812506666667</v>
+        <v>-65.41280246666665</v>
       </c>
       <c r="Q68">
-        <v>-62.86212506666667</v>
+        <v>-64.82680246666665</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1183131829422188</v>
+        <v>0.120510552122286</v>
       </c>
       <c r="T68">
-        <v>1.413416904260278</v>
+        <v>1.456247719540893</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.06383631809713211</v>
+        <v>0.06288353723001075</v>
       </c>
       <c r="W68">
-        <v>0.1879816673260959</v>
+        <v>0.1881729857242138</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5106905447770569</v>
+        <v>0.503068297840086</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1658443826355777</v>
+        <v>0.1913553456944748</v>
       </c>
       <c r="C69">
-        <v>-374.6424479942917</v>
+        <v>-442.6289683519872</v>
       </c>
       <c r="D69">
-        <v>367.9115520057082</v>
+        <v>311.1070316480128</v>
       </c>
       <c r="E69">
-        <v>129.894</v>
+        <v>141.076</v>
       </c>
       <c r="F69">
-        <v>749.194</v>
+        <v>760.376</v>
       </c>
       <c r="G69">
         <v>6.64</v>
@@ -6939,45 +6939,45 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M69">
-        <v>150.4381552</v>
+        <v>179.2966608</v>
       </c>
       <c r="N69">
-        <v>-74.75748853333332</v>
+        <v>-103.6159941333333</v>
       </c>
       <c r="O69">
-        <v>-9.344686066666664</v>
+        <v>-12.95199926666667</v>
       </c>
       <c r="P69">
-        <v>-65.41280246666665</v>
+        <v>-90.66399486666668</v>
       </c>
       <c r="Q69">
-        <v>-64.82680246666665</v>
+        <v>-90.07799486666669</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.120510552122286</v>
+        <v>0.1233482664351612</v>
       </c>
       <c r="T69">
-        <v>1.456247719540893</v>
+        <v>1.511560053333702</v>
       </c>
       <c r="U69">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.06288353723001075</v>
+        <v>0.05276218358514646</v>
       </c>
       <c r="W69">
-        <v>0.1881729857242138</v>
+        <v>0.2233586771106225</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y69">
-        <v>0.503068297840086</v>
+        <v>0.4220974686811717</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1913553456944748</v>
+        <v>0.1932553456944749</v>
       </c>
       <c r="C70">
-        <v>-442.6289683519872</v>
+        <v>-457.3477684940002</v>
       </c>
       <c r="D70">
-        <v>311.1070316480128</v>
+        <v>307.5702315059998</v>
       </c>
       <c r="E70">
-        <v>141.076</v>
+        <v>152.258</v>
       </c>
       <c r="F70">
-        <v>760.376</v>
+        <v>771.558</v>
       </c>
       <c r="G70">
         <v>6.64</v>
@@ -7021,37 +7021,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M70">
-        <v>179.2966608</v>
+        <v>181.9333764</v>
       </c>
       <c r="N70">
-        <v>-103.6159941333333</v>
+        <v>-106.2527097333333</v>
       </c>
       <c r="O70">
-        <v>-12.95199926666667</v>
+        <v>-13.28158871666667</v>
       </c>
       <c r="P70">
-        <v>-90.66399486666668</v>
+        <v>-92.97112101666667</v>
       </c>
       <c r="Q70">
-        <v>-90.07799486666669</v>
+        <v>-92.38512101666667</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1233482664351612</v>
+        <v>0.1258498234169406</v>
       </c>
       <c r="T70">
-        <v>1.511560053333702</v>
+        <v>1.560320055054145</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05276218358514646</v>
+        <v>0.0519975142578255</v>
       </c>
       <c r="W70">
-        <v>0.2233586771106225</v>
+        <v>0.2235389861380047</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4220974686811717</v>
+        <v>0.4159801140626039</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1932553456944749</v>
+        <v>0.1951553456944748</v>
       </c>
       <c r="C71">
-        <v>-457.3477684940002</v>
+        <v>-471.9870567944913</v>
       </c>
       <c r="D71">
-        <v>307.5702315059998</v>
+        <v>304.1129432055086</v>
       </c>
       <c r="E71">
-        <v>152.258</v>
+        <v>163.4399999999999</v>
       </c>
       <c r="F71">
-        <v>771.558</v>
+        <v>782.7399999999999</v>
       </c>
       <c r="G71">
         <v>6.64</v>
@@ -7103,37 +7103,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M71">
-        <v>181.9333764</v>
+        <v>184.570092</v>
       </c>
       <c r="N71">
-        <v>-106.2527097333333</v>
+        <v>-108.8894253333333</v>
       </c>
       <c r="O71">
-        <v>-13.28158871666667</v>
+        <v>-13.61117816666667</v>
       </c>
       <c r="P71">
-        <v>-92.97112101666667</v>
+        <v>-95.27824716666666</v>
       </c>
       <c r="Q71">
-        <v>-92.38512101666667</v>
+        <v>-94.69224716666666</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1258498234169406</v>
+        <v>0.1285181508641719</v>
       </c>
       <c r="T71">
-        <v>1.560320055054145</v>
+        <v>1.612330723555949</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0519975142578255</v>
+        <v>0.05125469262557086</v>
       </c>
       <c r="W71">
-        <v>0.2235389861380047</v>
+        <v>0.2237141434788904</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4159801140626039</v>
+        <v>0.4100375410045668</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1951553456944748</v>
+        <v>0.1970553456944749</v>
       </c>
       <c r="C72">
-        <v>-471.9870567944913</v>
+        <v>-486.54948474256</v>
       </c>
       <c r="D72">
-        <v>304.1129432055086</v>
+        <v>300.7325152574399</v>
       </c>
       <c r="E72">
-        <v>163.4399999999999</v>
+        <v>174.622</v>
       </c>
       <c r="F72">
-        <v>782.7399999999999</v>
+        <v>793.9219999999999</v>
       </c>
       <c r="G72">
         <v>6.64</v>
@@ -7185,37 +7185,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M72">
-        <v>184.570092</v>
+        <v>187.2068076</v>
       </c>
       <c r="N72">
-        <v>-108.8894253333333</v>
+        <v>-111.5261409333333</v>
       </c>
       <c r="O72">
-        <v>-13.61117816666667</v>
+        <v>-13.94076761666667</v>
       </c>
       <c r="P72">
-        <v>-95.27824716666666</v>
+        <v>-97.58537331666666</v>
       </c>
       <c r="Q72">
-        <v>-94.69224716666666</v>
+        <v>-96.99937331666666</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1285181508641719</v>
+        <v>0.131370500893971</v>
       </c>
       <c r="T72">
-        <v>1.612330723555949</v>
+        <v>1.667928334713051</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05125469262557086</v>
+        <v>0.05053279554633746</v>
       </c>
       <c r="W72">
-        <v>0.2237141434788904</v>
+        <v>0.2238843668101736</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4100375410045668</v>
+        <v>0.4042623643706997</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1970553456944748</v>
+        <v>0.1989553456944748</v>
       </c>
       <c r="C73">
-        <v>-486.5494847425599</v>
+        <v>-501.0375872307385</v>
       </c>
       <c r="D73">
-        <v>300.7325152574399</v>
+        <v>297.4264127692613</v>
       </c>
       <c r="E73">
-        <v>174.6219999999998</v>
+        <v>185.8039999999999</v>
       </c>
       <c r="F73">
-        <v>793.9219999999998</v>
+        <v>805.1039999999998</v>
       </c>
       <c r="G73">
         <v>6.64</v>
@@ -7267,37 +7267,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M73">
-        <v>187.2068076</v>
+        <v>189.8435232</v>
       </c>
       <c r="N73">
-        <v>-111.5261409333333</v>
+        <v>-114.1628565333333</v>
       </c>
       <c r="O73">
-        <v>-13.94076761666666</v>
+        <v>-14.27035706666666</v>
       </c>
       <c r="P73">
-        <v>-97.58537331666663</v>
+        <v>-99.89249946666664</v>
       </c>
       <c r="Q73">
-        <v>-96.99937331666663</v>
+        <v>-99.30649946666664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1313705008939709</v>
+        <v>0.1344265902116127</v>
       </c>
       <c r="T73">
-        <v>1.66792833471305</v>
+        <v>1.727497203809945</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05053279554633747</v>
+        <v>0.04983095116374945</v>
       </c>
       <c r="W73">
-        <v>0.2238843668101736</v>
+        <v>0.2240498617155879</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4042623643706997</v>
+        <v>0.3986476093099955</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1989553456944748</v>
+        <v>0.2008553456944748</v>
       </c>
       <c r="C74">
-        <v>-501.0375872307385</v>
+        <v>-515.4537888943219</v>
       </c>
       <c r="D74">
-        <v>297.4264127692613</v>
+        <v>294.1922111056779</v>
       </c>
       <c r="E74">
-        <v>185.8039999999999</v>
+        <v>196.9859999999999</v>
       </c>
       <c r="F74">
-        <v>805.1039999999998</v>
+        <v>816.2859999999998</v>
       </c>
       <c r="G74">
         <v>6.64</v>
@@ -7349,37 +7349,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M74">
-        <v>189.8435232</v>
+        <v>192.4802388</v>
       </c>
       <c r="N74">
-        <v>-114.1628565333333</v>
+        <v>-116.7995721333333</v>
       </c>
       <c r="O74">
-        <v>-14.27035706666666</v>
+        <v>-14.59994651666666</v>
       </c>
       <c r="P74">
-        <v>-99.89249946666664</v>
+        <v>-102.1996256166666</v>
       </c>
       <c r="Q74">
-        <v>-99.30649946666664</v>
+        <v>-101.6136256166666</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1344265902116127</v>
+        <v>0.1377090565157465</v>
       </c>
       <c r="T74">
-        <v>1.727497203809945</v>
+        <v>1.791478581728832</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04983095116374945</v>
+        <v>0.04914833539438301</v>
       </c>
       <c r="W74">
-        <v>0.2240498617155879</v>
+        <v>0.2242108225140045</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3986476093099955</v>
+        <v>0.3931866831550641</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2008553456944748</v>
+        <v>0.2027553456944748</v>
       </c>
       <c r="C75">
-        <v>-515.4537888943219</v>
+        <v>-529.800410041545</v>
       </c>
       <c r="D75">
-        <v>294.1922111056779</v>
+        <v>291.0275899584549</v>
       </c>
       <c r="E75">
-        <v>196.9859999999999</v>
+        <v>208.1679999999999</v>
       </c>
       <c r="F75">
-        <v>816.2859999999998</v>
+        <v>827.4679999999998</v>
       </c>
       <c r="G75">
         <v>6.64</v>
@@ -7431,37 +7431,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M75">
-        <v>192.4802388</v>
+        <v>195.1169544</v>
       </c>
       <c r="N75">
-        <v>-116.7995721333333</v>
+        <v>-119.4362877333333</v>
       </c>
       <c r="O75">
-        <v>-14.59994651666666</v>
+        <v>-14.92953596666666</v>
       </c>
       <c r="P75">
-        <v>-102.1996256166666</v>
+        <v>-104.5067517666666</v>
       </c>
       <c r="Q75">
-        <v>-101.6136256166666</v>
+        <v>-103.9207517666666</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1377090565157465</v>
+        <v>0.1412440202278906</v>
       </c>
       <c r="T75">
-        <v>1.791478581728832</v>
+        <v>1.860381604103018</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04914833539438301</v>
+        <v>0.04848416869986433</v>
       </c>
       <c r="W75">
-        <v>0.2242108225140045</v>
+        <v>0.224367433020572</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3931866831550641</v>
+        <v>0.3878733495989146</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2027553456944748</v>
+        <v>0.2046553456944749</v>
       </c>
       <c r="C76">
-        <v>-529.800410041545</v>
+        <v>-544.0796722050879</v>
       </c>
       <c r="D76">
-        <v>291.0275899584549</v>
+        <v>287.9303277949119</v>
       </c>
       <c r="E76">
-        <v>208.1679999999999</v>
+        <v>219.3499999999999</v>
       </c>
       <c r="F76">
-        <v>827.4679999999998</v>
+        <v>838.6499999999999</v>
       </c>
       <c r="G76">
         <v>6.64</v>
@@ -7513,37 +7513,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M76">
-        <v>195.1169544</v>
+        <v>197.75367</v>
       </c>
       <c r="N76">
-        <v>-119.4362877333333</v>
+        <v>-122.0730033333333</v>
       </c>
       <c r="O76">
-        <v>-14.92953596666666</v>
+        <v>-15.25912541666666</v>
       </c>
       <c r="P76">
-        <v>-104.5067517666666</v>
+        <v>-106.8138779166666</v>
       </c>
       <c r="Q76">
-        <v>-103.9207517666666</v>
+        <v>-106.2278779166666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1412440202278906</v>
+        <v>0.1450617810370063</v>
       </c>
       <c r="T76">
-        <v>1.860381604103018</v>
+        <v>1.934796868267139</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04848416869986433</v>
+        <v>0.04783771311719947</v>
       </c>
       <c r="W76">
-        <v>0.224367433020572</v>
+        <v>0.2245198672469644</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3878733495989146</v>
+        <v>0.3827017049375957</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2046553456944749</v>
+        <v>0.2065553456944749</v>
       </c>
       <c r="C77">
-        <v>-544.0796722050879</v>
+        <v>-558.2937033428234</v>
       </c>
       <c r="D77">
-        <v>287.9303277949119</v>
+        <v>284.8982966571765</v>
       </c>
       <c r="E77">
-        <v>219.3499999999999</v>
+        <v>230.5319999999999</v>
       </c>
       <c r="F77">
-        <v>838.6499999999999</v>
+        <v>849.8319999999999</v>
       </c>
       <c r="G77">
         <v>6.64</v>
@@ -7595,37 +7595,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M77">
-        <v>197.75367</v>
+        <v>200.3903856</v>
       </c>
       <c r="N77">
-        <v>-122.0730033333333</v>
+        <v>-124.7097189333333</v>
       </c>
       <c r="O77">
-        <v>-15.25912541666666</v>
+        <v>-15.58871486666666</v>
       </c>
       <c r="P77">
-        <v>-106.8138779166666</v>
+        <v>-109.1210040666666</v>
       </c>
       <c r="Q77">
-        <v>-106.2278779166666</v>
+        <v>-108.5350040666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1450617810370063</v>
+        <v>0.1491976885802149</v>
       </c>
       <c r="T77">
-        <v>1.934796868267139</v>
+        <v>2.015413404444936</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04783771311719947</v>
+        <v>0.04720826952355211</v>
       </c>
       <c r="W77">
-        <v>0.2245198672469644</v>
+        <v>0.2246682900463464</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3827017049375957</v>
+        <v>0.3776661561884168</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2065553456944749</v>
+        <v>0.2084553456944749</v>
       </c>
       <c r="C78">
-        <v>-558.2937033428234</v>
+        <v>-572.4445427133904</v>
       </c>
       <c r="D78">
-        <v>284.8982966571765</v>
+        <v>281.9294572866095</v>
       </c>
       <c r="E78">
-        <v>230.5319999999999</v>
+        <v>241.7139999999999</v>
       </c>
       <c r="F78">
-        <v>849.8319999999999</v>
+        <v>861.0139999999999</v>
       </c>
       <c r="G78">
         <v>6.64</v>
@@ -7677,37 +7677,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M78">
-        <v>200.3903856</v>
+        <v>203.0271012</v>
       </c>
       <c r="N78">
-        <v>-124.7097189333333</v>
+        <v>-127.3464345333333</v>
       </c>
       <c r="O78">
-        <v>-15.58871486666666</v>
+        <v>-15.91830431666666</v>
       </c>
       <c r="P78">
-        <v>-109.1210040666666</v>
+        <v>-111.4281302166666</v>
       </c>
       <c r="Q78">
-        <v>-108.5350040666666</v>
+        <v>-110.8421302166666</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1491976885802149</v>
+        <v>0.1536932402576155</v>
       </c>
       <c r="T78">
-        <v>2.015413404444936</v>
+        <v>2.103040074203411</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04720826952355211</v>
+        <v>0.04659517511415533</v>
       </c>
       <c r="W78">
-        <v>0.2246682900463464</v>
+        <v>0.2248128577080822</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3776661561884168</v>
+        <v>0.3727614009132426</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2084553456944749</v>
+        <v>0.2103553456944748</v>
       </c>
       <c r="C79">
-        <v>-572.4445427133904</v>
+        <v>-586.5341454500724</v>
       </c>
       <c r="D79">
-        <v>281.9294572866095</v>
+        <v>279.0218545499275</v>
       </c>
       <c r="E79">
-        <v>241.7139999999999</v>
+        <v>252.896</v>
       </c>
       <c r="F79">
-        <v>861.0139999999999</v>
+        <v>872.1959999999999</v>
       </c>
       <c r="G79">
         <v>6.64</v>
@@ -7759,37 +7759,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M79">
-        <v>203.0271012</v>
+        <v>205.6638168</v>
       </c>
       <c r="N79">
-        <v>-127.3464345333333</v>
+        <v>-129.9831501333333</v>
       </c>
       <c r="O79">
-        <v>-15.91830431666666</v>
+        <v>-16.24789376666666</v>
       </c>
       <c r="P79">
-        <v>-111.4281302166666</v>
+        <v>-113.7352563666666</v>
       </c>
       <c r="Q79">
-        <v>-110.8421302166666</v>
+        <v>-113.1492563666666</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1536932402576155</v>
+        <v>0.1585974784511435</v>
       </c>
       <c r="T79">
-        <v>2.103040074203411</v>
+        <v>2.198632804849022</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04659517511415533</v>
+        <v>0.04599780107423025</v>
       </c>
       <c r="W79">
-        <v>0.2248128577080822</v>
+        <v>0.2249537185066965</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3727614009132426</v>
+        <v>0.367982408593842</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2103553456944748</v>
+        <v>0.2122553456944749</v>
       </c>
       <c r="C80">
-        <v>-586.5341454500724</v>
+        <v>-600.5643868545342</v>
       </c>
       <c r="D80">
-        <v>279.0218545499275</v>
+        <v>276.1736131454658</v>
       </c>
       <c r="E80">
-        <v>252.896</v>
+        <v>264.078</v>
       </c>
       <c r="F80">
-        <v>872.1959999999999</v>
+        <v>883.3779999999999</v>
       </c>
       <c r="G80">
         <v>6.64</v>
@@ -7841,37 +7841,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M80">
-        <v>205.6638168</v>
+        <v>208.3005324</v>
       </c>
       <c r="N80">
-        <v>-129.9831501333333</v>
+        <v>-132.6198657333333</v>
       </c>
       <c r="O80">
-        <v>-16.24789376666666</v>
+        <v>-16.57748321666666</v>
       </c>
       <c r="P80">
-        <v>-113.7352563666666</v>
+        <v>-116.0423825166666</v>
       </c>
       <c r="Q80">
-        <v>-113.1492563666666</v>
+        <v>-115.4563825166667</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1585974784511435</v>
+        <v>0.163968786948817</v>
       </c>
       <c r="T80">
-        <v>2.198632804849022</v>
+        <v>2.303329605079927</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04599780107423025</v>
+        <v>0.04541555042772101</v>
       </c>
       <c r="W80">
-        <v>0.2249537185066965</v>
+        <v>0.2250910132091434</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.367982408593842</v>
+        <v>0.3633244034217681</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2122553456944749</v>
+        <v>0.2141553456944748</v>
       </c>
       <c r="C81">
-        <v>-600.5643868545342</v>
+        <v>-614.5370664302347</v>
       </c>
       <c r="D81">
-        <v>276.1736131454658</v>
+        <v>273.3829335697652</v>
       </c>
       <c r="E81">
-        <v>264.078</v>
+        <v>275.26</v>
       </c>
       <c r="F81">
-        <v>883.3779999999999</v>
+        <v>894.5599999999999</v>
       </c>
       <c r="G81">
         <v>6.64</v>
@@ -7923,37 +7923,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M81">
-        <v>208.3005324</v>
+        <v>210.937248</v>
       </c>
       <c r="N81">
-        <v>-132.6198657333333</v>
+        <v>-135.2565813333333</v>
       </c>
       <c r="O81">
-        <v>-16.57748321666666</v>
+        <v>-16.90707266666666</v>
       </c>
       <c r="P81">
-        <v>-116.0423825166666</v>
+        <v>-118.3495086666667</v>
       </c>
       <c r="Q81">
-        <v>-115.4563825166667</v>
+        <v>-117.7635086666667</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.163968786948817</v>
+        <v>0.1698772262962579</v>
       </c>
       <c r="T81">
-        <v>2.303329605079927</v>
+        <v>2.418496085333924</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04541555042772101</v>
+        <v>0.0448478560473745</v>
       </c>
       <c r="W81">
-        <v>0.2250910132091434</v>
+        <v>0.2252248755440291</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3633244034217681</v>
+        <v>0.358782848378996</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2141553456944748</v>
+        <v>0.2160553456944749</v>
       </c>
       <c r="C82">
-        <v>-614.5370664302347</v>
+        <v>-628.4539116737474</v>
       </c>
       <c r="D82">
-        <v>273.3829335697652</v>
+        <v>270.6480883262527</v>
       </c>
       <c r="E82">
-        <v>275.26</v>
+        <v>286.442</v>
       </c>
       <c r="F82">
-        <v>894.5599999999999</v>
+        <v>905.742</v>
       </c>
       <c r="G82">
         <v>6.64</v>
@@ -8005,37 +8005,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M82">
-        <v>210.937248</v>
+        <v>213.5739636</v>
       </c>
       <c r="N82">
-        <v>-135.2565813333333</v>
+        <v>-137.8932969333333</v>
       </c>
       <c r="O82">
-        <v>-16.90707266666666</v>
+        <v>-17.23666211666667</v>
       </c>
       <c r="P82">
-        <v>-118.3495086666667</v>
+        <v>-120.6566348166667</v>
       </c>
       <c r="Q82">
-        <v>-117.7635086666667</v>
+        <v>-120.0706348166667</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1698772262962579</v>
+        <v>0.1764076066276399</v>
       </c>
       <c r="T82">
-        <v>2.418496085333924</v>
+        <v>2.545785352983078</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.0448478560473745</v>
+        <v>0.04429417881222172</v>
       </c>
       <c r="W82">
-        <v>0.2252248755440291</v>
+        <v>0.2253554326360781</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.358782848378996</v>
+        <v>0.3543534304977738</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2160553456944749</v>
+        <v>0.2179553456944749</v>
       </c>
       <c r="C83">
-        <v>-628.4539116737474</v>
+        <v>-642.3165816407661</v>
       </c>
       <c r="D83">
-        <v>270.6480883262527</v>
+        <v>267.9674183592337</v>
       </c>
       <c r="E83">
-        <v>286.442</v>
+        <v>297.6239999999999</v>
       </c>
       <c r="F83">
-        <v>905.742</v>
+        <v>916.9239999999999</v>
       </c>
       <c r="G83">
         <v>6.64</v>
@@ -8087,37 +8087,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M83">
-        <v>213.5739636</v>
+        <v>216.2106792</v>
       </c>
       <c r="N83">
-        <v>-137.8932969333333</v>
+        <v>-140.5300125333333</v>
       </c>
       <c r="O83">
-        <v>-17.23666211666667</v>
+        <v>-17.56625156666666</v>
       </c>
       <c r="P83">
-        <v>-120.6566348166667</v>
+        <v>-122.9637609666667</v>
       </c>
       <c r="Q83">
-        <v>-120.0706348166667</v>
+        <v>-122.3777609666667</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1764076066276399</v>
+        <v>0.1836635847736199</v>
       </c>
       <c r="T83">
-        <v>2.545785352983078</v>
+        <v>2.687217872593249</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04429417881222172</v>
+        <v>0.04375400589987756</v>
       </c>
       <c r="W83">
-        <v>0.2253554326360781</v>
+        <v>0.2254828054088089</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3543534304977738</v>
+        <v>0.3500320471990205</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2179553456944749</v>
+        <v>0.2198553456944748</v>
       </c>
       <c r="C84">
-        <v>-642.3165816407661</v>
+        <v>-656.1266703022766</v>
       </c>
       <c r="D84">
-        <v>267.9674183592337</v>
+        <v>265.3393296977234</v>
       </c>
       <c r="E84">
-        <v>297.6239999999999</v>
+        <v>308.8059999999999</v>
       </c>
       <c r="F84">
-        <v>916.9239999999999</v>
+        <v>928.1059999999999</v>
       </c>
       <c r="G84">
         <v>6.64</v>
@@ -8169,37 +8169,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M84">
-        <v>216.2106792</v>
+        <v>218.8473948</v>
       </c>
       <c r="N84">
-        <v>-140.5300125333333</v>
+        <v>-143.1667281333333</v>
       </c>
       <c r="O84">
-        <v>-17.56625156666666</v>
+        <v>-17.89584101666667</v>
       </c>
       <c r="P84">
-        <v>-122.9637609666667</v>
+        <v>-125.2708871166667</v>
       </c>
       <c r="Q84">
-        <v>-122.3777609666667</v>
+        <v>-124.6848871166667</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1836635847736199</v>
+        <v>0.1917732074073622</v>
       </c>
       <c r="T84">
-        <v>2.687217872593249</v>
+        <v>2.845289512157557</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04375400589987756</v>
+        <v>0.04322684920228867</v>
       </c>
       <c r="W84">
-        <v>0.2254828054088089</v>
+        <v>0.2256071089581003</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3500320471990205</v>
+        <v>0.3458147936183094</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2198553456944748</v>
+        <v>0.2217553456944749</v>
       </c>
       <c r="C85">
-        <v>-656.1266703022766</v>
+        <v>-669.8857097051439</v>
       </c>
       <c r="D85">
-        <v>265.3393296977234</v>
+        <v>262.762290294856</v>
       </c>
       <c r="E85">
-        <v>308.8059999999999</v>
+        <v>319.9879999999999</v>
       </c>
       <c r="F85">
-        <v>928.1059999999999</v>
+        <v>939.2879999999999</v>
       </c>
       <c r="G85">
         <v>6.64</v>
@@ -8251,37 +8251,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M85">
-        <v>218.8473948</v>
+        <v>221.4841104</v>
       </c>
       <c r="N85">
-        <v>-143.1667281333333</v>
+        <v>-145.8034437333333</v>
       </c>
       <c r="O85">
-        <v>-17.89584101666667</v>
+        <v>-18.22543046666667</v>
       </c>
       <c r="P85">
-        <v>-125.2708871166667</v>
+        <v>-127.5780132666667</v>
       </c>
       <c r="Q85">
-        <v>-124.6848871166667</v>
+        <v>-126.9920132666667</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1917732074073622</v>
+        <v>0.2008965328703224</v>
       </c>
       <c r="T85">
-        <v>2.845289512157557</v>
+        <v>3.023120106667406</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04322684920228867</v>
+        <v>0.04271224385464237</v>
       </c>
       <c r="W85">
-        <v>0.2256071089581003</v>
+        <v>0.2257284528990753</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3458147936183094</v>
+        <v>0.3416979508371391</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2217553456944749</v>
+        <v>0.2236553456944748</v>
       </c>
       <c r="C86">
-        <v>-669.8857097051438</v>
+        <v>-683.5951729503001</v>
       </c>
       <c r="D86">
-        <v>262.762290294856</v>
+        <v>260.2348270496997</v>
       </c>
       <c r="E86">
-        <v>319.9879999999998</v>
+        <v>331.1699999999998</v>
       </c>
       <c r="F86">
-        <v>939.2879999999998</v>
+        <v>950.4699999999998</v>
       </c>
       <c r="G86">
         <v>6.64</v>
@@ -8333,37 +8333,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M86">
-        <v>221.4841104</v>
+        <v>224.120826</v>
       </c>
       <c r="N86">
-        <v>-145.8034437333333</v>
+        <v>-148.4401593333333</v>
       </c>
       <c r="O86">
-        <v>-18.22543046666666</v>
+        <v>-18.55501991666666</v>
       </c>
       <c r="P86">
-        <v>-127.5780132666666</v>
+        <v>-129.8851394166666</v>
       </c>
       <c r="Q86">
-        <v>-126.9920132666666</v>
+        <v>-129.2991394166666</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2008965328703223</v>
+        <v>0.2112363017283438</v>
       </c>
       <c r="T86">
-        <v>3.023120106667403</v>
+        <v>3.224661447111898</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04271224385464238</v>
+        <v>0.04220974686811717</v>
       </c>
       <c r="W86">
-        <v>0.2257284528990753</v>
+        <v>0.225846941688498</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3416979508371391</v>
+        <v>0.3376779749449375</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2236553456944748</v>
+        <v>0.2255553456944748</v>
       </c>
       <c r="C87">
-        <v>-683.5951729503001</v>
+        <v>-697.2564770006866</v>
       </c>
       <c r="D87">
-        <v>260.2348270496997</v>
+        <v>257.7555229993133</v>
       </c>
       <c r="E87">
-        <v>331.1699999999998</v>
+        <v>342.3519999999999</v>
       </c>
       <c r="F87">
-        <v>950.4699999999998</v>
+        <v>961.6519999999998</v>
       </c>
       <c r="G87">
         <v>6.64</v>
@@ -8415,37 +8415,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M87">
-        <v>224.120826</v>
+        <v>226.7575416</v>
       </c>
       <c r="N87">
-        <v>-148.4401593333333</v>
+        <v>-151.0768749333333</v>
       </c>
       <c r="O87">
-        <v>-18.55501991666666</v>
+        <v>-18.88460936666666</v>
       </c>
       <c r="P87">
-        <v>-129.8851394166666</v>
+        <v>-132.1922655666666</v>
       </c>
       <c r="Q87">
-        <v>-129.2991394166666</v>
+        <v>-131.6062655666666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2112363017283438</v>
+        <v>0.2230531804232255</v>
       </c>
       <c r="T87">
-        <v>3.224661447111898</v>
+        <v>3.45499440761989</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04220974686811717</v>
+        <v>0.04171893585802279</v>
       </c>
       <c r="W87">
-        <v>0.225846941688498</v>
+        <v>0.2259626749246782</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3376779749449375</v>
+        <v>0.3337514868641823</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2255553456944748</v>
+        <v>0.2274553456944748</v>
       </c>
       <c r="C88">
-        <v>-697.2564770006866</v>
+        <v>-710.8709853301993</v>
       </c>
       <c r="D88">
-        <v>257.7555229993133</v>
+        <v>255.3230146698004</v>
       </c>
       <c r="E88">
-        <v>342.3519999999999</v>
+        <v>353.5339999999999</v>
       </c>
       <c r="F88">
-        <v>961.6519999999998</v>
+        <v>972.8339999999998</v>
       </c>
       <c r="G88">
         <v>6.64</v>
@@ -8497,37 +8497,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M88">
-        <v>226.7575416</v>
+        <v>229.3942572</v>
       </c>
       <c r="N88">
-        <v>-151.0768749333333</v>
+        <v>-153.7135905333333</v>
       </c>
       <c r="O88">
-        <v>-18.88460936666666</v>
+        <v>-19.21419881666666</v>
       </c>
       <c r="P88">
-        <v>-132.1922655666666</v>
+        <v>-134.4993917166667</v>
       </c>
       <c r="Q88">
-        <v>-131.6062655666666</v>
+        <v>-133.9133917166666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2230531804232255</v>
+        <v>0.2366880404557813</v>
       </c>
       <c r="T88">
-        <v>3.45499440761989</v>
+        <v>3.720763208206035</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04171893585802279</v>
+        <v>0.04123940785965471</v>
       </c>
       <c r="W88">
-        <v>0.2259626749246782</v>
+        <v>0.2260757476266934</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3337514868641823</v>
+        <v>0.3299152628772377</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2274553456944748</v>
+        <v>0.2293553456944748</v>
       </c>
       <c r="C89">
-        <v>-710.8709853301993</v>
+        <v>-724.4400104240465</v>
       </c>
       <c r="D89">
-        <v>255.3230146698004</v>
+        <v>252.9359895759534</v>
       </c>
       <c r="E89">
-        <v>353.5339999999999</v>
+        <v>364.7159999999999</v>
       </c>
       <c r="F89">
-        <v>972.8339999999998</v>
+        <v>984.0159999999998</v>
       </c>
       <c r="G89">
         <v>6.64</v>
@@ -8579,37 +8579,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M89">
-        <v>229.3942572</v>
+        <v>232.0309728</v>
       </c>
       <c r="N89">
-        <v>-153.7135905333333</v>
+        <v>-156.3503061333333</v>
       </c>
       <c r="O89">
-        <v>-19.21419881666666</v>
+        <v>-19.54378826666666</v>
       </c>
       <c r="P89">
-        <v>-134.4993917166667</v>
+        <v>-136.8065178666666</v>
       </c>
       <c r="Q89">
-        <v>-133.9133917166666</v>
+        <v>-136.2205178666666</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2366880404557813</v>
+        <v>0.2525953771604297</v>
       </c>
       <c r="T89">
-        <v>3.720763208206035</v>
+        <v>4.030826808889872</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04123940785965471</v>
+        <v>0.04077077822488591</v>
       </c>
       <c r="W89">
-        <v>0.2260757476266934</v>
+        <v>0.2261862504945719</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3299152628772377</v>
+        <v>0.3261662257990873</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2293553456944748</v>
+        <v>0.2312553456944748</v>
       </c>
       <c r="C90">
-        <v>-724.4400104240465</v>
+        <v>-737.9648161401474</v>
       </c>
       <c r="D90">
-        <v>252.9359895759534</v>
+        <v>250.5931838598525</v>
       </c>
       <c r="E90">
-        <v>364.7159999999999</v>
+        <v>375.8979999999999</v>
       </c>
       <c r="F90">
-        <v>984.0159999999998</v>
+        <v>995.1979999999999</v>
       </c>
       <c r="G90">
         <v>6.64</v>
@@ -8661,37 +8661,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M90">
-        <v>232.0309728</v>
+        <v>234.6676884</v>
       </c>
       <c r="N90">
-        <v>-156.3503061333333</v>
+        <v>-158.9870217333333</v>
       </c>
       <c r="O90">
-        <v>-19.54378826666666</v>
+        <v>-19.87337771666666</v>
       </c>
       <c r="P90">
-        <v>-136.8065178666666</v>
+        <v>-139.1136440166667</v>
       </c>
       <c r="Q90">
-        <v>-136.2205178666666</v>
+        <v>-138.5276440166666</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2525953771604297</v>
+        <v>0.271394956902287</v>
       </c>
       <c r="T90">
-        <v>4.030826808889872</v>
+        <v>4.397265609698043</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04077077822488591</v>
+        <v>0.04031267959314562</v>
       </c>
       <c r="W90">
-        <v>0.2261862504945719</v>
+        <v>0.2262942701519363</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3261662257990873</v>
+        <v>0.322501436745165</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2312553456944748</v>
+        <v>0.2331553456944749</v>
       </c>
       <c r="C91">
-        <v>-737.9648161401474</v>
+        <v>-751.4466199405027</v>
       </c>
       <c r="D91">
-        <v>250.5931838598525</v>
+        <v>248.2933800594972</v>
       </c>
       <c r="E91">
-        <v>375.8979999999999</v>
+        <v>387.0799999999999</v>
       </c>
       <c r="F91">
-        <v>995.1979999999999</v>
+        <v>1006.38</v>
       </c>
       <c r="G91">
         <v>6.64</v>
@@ -8743,37 +8743,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M91">
-        <v>234.6676884</v>
+        <v>237.304404</v>
       </c>
       <c r="N91">
-        <v>-158.9870217333333</v>
+        <v>-161.6237373333333</v>
       </c>
       <c r="O91">
-        <v>-19.87337771666666</v>
+        <v>-20.20296716666666</v>
       </c>
       <c r="P91">
-        <v>-139.1136440166667</v>
+        <v>-141.4207701666666</v>
       </c>
       <c r="Q91">
-        <v>-138.5276440166666</v>
+        <v>-140.8347701666666</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.271394956902287</v>
+        <v>0.2939544525925157</v>
       </c>
       <c r="T91">
-        <v>4.397265609698043</v>
+        <v>4.836992170667847</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04031267959314562</v>
+        <v>0.03986476093099955</v>
       </c>
       <c r="W91">
-        <v>0.2262942701519363</v>
+        <v>0.2263998893724703</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.322501436745165</v>
+        <v>0.3189180874479964</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2331553456944749</v>
+        <v>0.2350553456944748</v>
       </c>
       <c r="C92">
-        <v>-751.4466199405027</v>
+        <v>-764.8865950008121</v>
       </c>
       <c r="D92">
-        <v>248.2933800594972</v>
+        <v>246.0354049991878</v>
       </c>
       <c r="E92">
-        <v>387.0799999999999</v>
+        <v>398.2619999999999</v>
       </c>
       <c r="F92">
-        <v>1006.38</v>
+        <v>1017.562</v>
       </c>
       <c r="G92">
         <v>6.64</v>
@@ -8825,37 +8825,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M92">
-        <v>237.304404</v>
+        <v>239.9411196</v>
       </c>
       <c r="N92">
-        <v>-161.6237373333333</v>
+        <v>-164.2604529333333</v>
       </c>
       <c r="O92">
-        <v>-20.20296716666666</v>
+        <v>-20.53255661666666</v>
       </c>
       <c r="P92">
-        <v>-141.4207701666666</v>
+        <v>-143.7278963166667</v>
       </c>
       <c r="Q92">
-        <v>-140.8347701666666</v>
+        <v>-143.1418963166666</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2939544525925157</v>
+        <v>0.3215271695472397</v>
       </c>
       <c r="T92">
-        <v>4.836992170667847</v>
+        <v>5.374435745186497</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03986476093099955</v>
+        <v>0.0394266866350545</v>
       </c>
       <c r="W92">
-        <v>0.2263998893724703</v>
+        <v>0.2265031872914541</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3189180874479964</v>
+        <v>0.315413493080436</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2350553456944748</v>
+        <v>0.2369553456944749</v>
       </c>
       <c r="C93">
-        <v>-764.8865950008121</v>
+        <v>-778.2858722060208</v>
       </c>
       <c r="D93">
-        <v>246.0354049991878</v>
+        <v>243.8181277939791</v>
       </c>
       <c r="E93">
-        <v>398.2619999999999</v>
+        <v>409.444</v>
       </c>
       <c r="F93">
-        <v>1017.562</v>
+        <v>1028.744</v>
       </c>
       <c r="G93">
         <v>6.64</v>
@@ -8907,37 +8907,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M93">
-        <v>239.9411196</v>
+        <v>242.5778352</v>
       </c>
       <c r="N93">
-        <v>-164.2604529333333</v>
+        <v>-166.8971685333333</v>
       </c>
       <c r="O93">
-        <v>-20.53255661666666</v>
+        <v>-20.86214606666666</v>
       </c>
       <c r="P93">
-        <v>-143.7278963166667</v>
+        <v>-146.0350224666666</v>
       </c>
       <c r="Q93">
-        <v>-143.1418963166666</v>
+        <v>-145.4490224666666</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3215271695472397</v>
+        <v>0.3559930657406448</v>
       </c>
       <c r="T93">
-        <v>5.374435745186497</v>
+        <v>6.046240213334811</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.0394266866350545</v>
+        <v>0.03899813569336913</v>
       </c>
       <c r="W93">
-        <v>0.2265031872914541</v>
+        <v>0.2266042396035036</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.315413493080436</v>
+        <v>0.311985085546953</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2369553456944749</v>
+        <v>0.2388553456944749</v>
       </c>
       <c r="C94">
-        <v>-778.2858722060208</v>
+        <v>-791.6455420389258</v>
       </c>
       <c r="D94">
-        <v>243.8181277939791</v>
+        <v>241.6404579610742</v>
       </c>
       <c r="E94">
-        <v>409.444</v>
+        <v>420.626</v>
       </c>
       <c r="F94">
-        <v>1028.744</v>
+        <v>1039.926</v>
       </c>
       <c r="G94">
         <v>6.64</v>
@@ -8989,37 +8989,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M94">
-        <v>242.5778352</v>
+        <v>245.2145508</v>
       </c>
       <c r="N94">
-        <v>-166.8971685333333</v>
+        <v>-169.5338841333333</v>
       </c>
       <c r="O94">
-        <v>-20.86214606666666</v>
+        <v>-21.19173551666666</v>
       </c>
       <c r="P94">
-        <v>-146.0350224666666</v>
+        <v>-148.3421486166667</v>
       </c>
       <c r="Q94">
-        <v>-145.4490224666666</v>
+        <v>-147.7561486166666</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3559930657406448</v>
+        <v>0.4003063608464512</v>
       </c>
       <c r="T94">
-        <v>6.046240213334811</v>
+        <v>6.909988815239785</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03899813569336913</v>
+        <v>0.03857880090096731</v>
       </c>
       <c r="W94">
-        <v>0.2266042396035036</v>
+        <v>0.2267031187475519</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.311985085546953</v>
+        <v>0.3086304072077385</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2388553456944749</v>
+        <v>0.2407553456944748</v>
       </c>
       <c r="C95">
-        <v>-791.6455420389258</v>
+        <v>-804.9666563684693</v>
       </c>
       <c r="D95">
-        <v>241.6404579610742</v>
+        <v>239.5013436315307</v>
       </c>
       <c r="E95">
-        <v>420.626</v>
+        <v>431.808</v>
       </c>
       <c r="F95">
-        <v>1039.926</v>
+        <v>1051.108</v>
       </c>
       <c r="G95">
         <v>6.64</v>
@@ -9071,37 +9071,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M95">
-        <v>245.2145508</v>
+        <v>247.8512664</v>
       </c>
       <c r="N95">
-        <v>-169.5338841333333</v>
+        <v>-172.1705997333333</v>
       </c>
       <c r="O95">
-        <v>-21.19173551666666</v>
+        <v>-21.52132496666666</v>
       </c>
       <c r="P95">
-        <v>-148.3421486166667</v>
+        <v>-150.6492747666667</v>
       </c>
       <c r="Q95">
-        <v>-147.7561486166666</v>
+        <v>-150.0632747666666</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4003063608464512</v>
+        <v>0.4593907543208598</v>
       </c>
       <c r="T95">
-        <v>6.909988815239785</v>
+        <v>8.061653617779751</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03857880090096731</v>
+        <v>0.03816838812542511</v>
       </c>
       <c r="W95">
-        <v>0.2267031187475519</v>
+        <v>0.2267998940800248</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3086304072077385</v>
+        <v>0.3053471050034008</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2407553456944748</v>
+        <v>0.2426553456944749</v>
       </c>
       <c r="C96">
-        <v>-804.9666563684693</v>
+        <v>-818.2502301438815</v>
       </c>
       <c r="D96">
-        <v>239.5013436315307</v>
+        <v>237.3997698561186</v>
       </c>
       <c r="E96">
-        <v>431.808</v>
+        <v>442.99</v>
       </c>
       <c r="F96">
-        <v>1051.108</v>
+        <v>1062.29</v>
       </c>
       <c r="G96">
         <v>6.64</v>
@@ -9153,37 +9153,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M96">
-        <v>247.8512664</v>
+        <v>250.487982</v>
       </c>
       <c r="N96">
-        <v>-172.1705997333333</v>
+        <v>-174.8073153333333</v>
       </c>
       <c r="O96">
-        <v>-21.52132496666666</v>
+        <v>-21.85091441666667</v>
       </c>
       <c r="P96">
-        <v>-150.6492747666667</v>
+        <v>-152.9564009166667</v>
       </c>
       <c r="Q96">
-        <v>-150.0632747666666</v>
+        <v>-152.3704009166667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4593907543208598</v>
+        <v>0.542108905185032</v>
       </c>
       <c r="T96">
-        <v>8.061653617779751</v>
+        <v>9.673984341335705</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03816838812542511</v>
+        <v>0.03776661561884168</v>
       </c>
       <c r="W96">
-        <v>0.2267998940800248</v>
+        <v>0.2268946320370772</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3053471050034008</v>
+        <v>0.3021329249507334</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2426553456944749</v>
+        <v>0.2445553456944749</v>
       </c>
       <c r="C97">
-        <v>-818.2502301438815</v>
+        <v>-831.4972430004032</v>
       </c>
       <c r="D97">
-        <v>237.3997698561186</v>
+        <v>235.3347569995968</v>
       </c>
       <c r="E97">
-        <v>442.99</v>
+        <v>454.172</v>
       </c>
       <c r="F97">
-        <v>1062.29</v>
+        <v>1073.472</v>
       </c>
       <c r="G97">
         <v>6.64</v>
@@ -9235,37 +9235,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M97">
-        <v>250.487982</v>
+        <v>253.1246976</v>
       </c>
       <c r="N97">
-        <v>-174.8073153333333</v>
+        <v>-177.4440309333334</v>
       </c>
       <c r="O97">
-        <v>-21.85091441666667</v>
+        <v>-22.18050386666667</v>
       </c>
       <c r="P97">
-        <v>-152.9564009166667</v>
+        <v>-155.2635270666667</v>
       </c>
       <c r="Q97">
-        <v>-152.3704009166667</v>
+        <v>-154.6775270666667</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.542108905185032</v>
+        <v>0.6661861314812904</v>
       </c>
       <c r="T97">
-        <v>9.673984341335705</v>
+        <v>12.09248042666964</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03776661561884168</v>
+        <v>0.03737321337281208</v>
       </c>
       <c r="W97">
-        <v>0.2268946320370772</v>
+        <v>0.2269873962866909</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3021329249507334</v>
+        <v>0.2989857069824966</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2445553456944748</v>
+        <v>0.2464553456944749</v>
       </c>
       <c r="C98">
-        <v>-831.4972430004029</v>
+        <v>-844.7086407819286</v>
       </c>
       <c r="D98">
-        <v>235.3347569995968</v>
+        <v>233.3053592180711</v>
       </c>
       <c r="E98">
-        <v>454.1719999999998</v>
+        <v>465.3539999999998</v>
       </c>
       <c r="F98">
-        <v>1073.472</v>
+        <v>1084.654</v>
       </c>
       <c r="G98">
         <v>6.64</v>
@@ -9317,37 +9317,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M98">
-        <v>253.1246976</v>
+        <v>255.7614132</v>
       </c>
       <c r="N98">
-        <v>-177.4440309333333</v>
+        <v>-180.0807465333333</v>
       </c>
       <c r="O98">
-        <v>-22.18050386666666</v>
+        <v>-22.51009331666666</v>
       </c>
       <c r="P98">
-        <v>-155.2635270666666</v>
+        <v>-157.5706532166666</v>
       </c>
       <c r="Q98">
-        <v>-154.6775270666666</v>
+        <v>-156.9846532166666</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6661861314812886</v>
+        <v>0.8729815086417183</v>
       </c>
       <c r="T98">
-        <v>12.0924804266696</v>
+        <v>16.12330723555948</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03737321337281208</v>
+        <v>0.03698792251329856</v>
       </c>
       <c r="W98">
-        <v>0.2269873962866909</v>
+        <v>0.2270782478713642</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2989857069824967</v>
+        <v>0.2959033801063885</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2464553456944749</v>
+        <v>0.2483553456944748</v>
       </c>
       <c r="C99">
-        <v>-844.7086407819286</v>
+        <v>-857.8853369855397</v>
       </c>
       <c r="D99">
-        <v>233.3053592180711</v>
+        <v>231.3106630144602</v>
       </c>
       <c r="E99">
-        <v>465.3539999999998</v>
+        <v>476.5359999999998</v>
       </c>
       <c r="F99">
-        <v>1084.654</v>
+        <v>1095.836</v>
       </c>
       <c r="G99">
         <v>6.64</v>
@@ -9399,37 +9399,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M99">
-        <v>255.7614132</v>
+        <v>258.3981287999999</v>
       </c>
       <c r="N99">
-        <v>-180.0807465333333</v>
+        <v>-182.7174621333333</v>
       </c>
       <c r="O99">
-        <v>-22.51009331666666</v>
+        <v>-22.83968276666666</v>
       </c>
       <c r="P99">
-        <v>-157.5706532166666</v>
+        <v>-159.8777793666666</v>
       </c>
       <c r="Q99">
-        <v>-156.9846532166666</v>
+        <v>-159.2917793666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8729815086417183</v>
+        <v>1.286572262962577</v>
       </c>
       <c r="T99">
-        <v>16.12330723555948</v>
+        <v>24.18496085333921</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03698792251329856</v>
+        <v>0.03661049473255062</v>
       </c>
       <c r="W99">
-        <v>0.2270782478713642</v>
+        <v>0.2271672453420646</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2959033801063885</v>
+        <v>0.2928839578604049</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2483553456944748</v>
+        <v>0.2502553456944748</v>
       </c>
       <c r="C100">
-        <v>-857.8853369855397</v>
+        <v>-871.0282141325628</v>
       </c>
       <c r="D100">
-        <v>231.3106630144602</v>
+        <v>229.349785867437</v>
       </c>
       <c r="E100">
-        <v>476.5359999999998</v>
+        <v>487.7179999999998</v>
       </c>
       <c r="F100">
-        <v>1095.836</v>
+        <v>1107.018</v>
       </c>
       <c r="G100">
         <v>6.64</v>
@@ -9481,37 +9481,37 @@
         <v>75.68066666666667</v>
       </c>
       <c r="M100">
-        <v>258.3981287999999</v>
+        <v>261.0348443999999</v>
       </c>
       <c r="N100">
-        <v>-182.7174621333333</v>
+        <v>-185.3541777333333</v>
       </c>
       <c r="O100">
-        <v>-22.83968276666666</v>
+        <v>-23.16927221666666</v>
       </c>
       <c r="P100">
-        <v>-159.8777793666666</v>
+        <v>-162.1849055166666</v>
       </c>
       <c r="Q100">
-        <v>-159.2917793666666</v>
+        <v>-161.5989055166666</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.286572262962577</v>
+        <v>2.527344525925154</v>
       </c>
       <c r="T100">
-        <v>24.18496085333921</v>
+        <v>48.36992170667842</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03661049473255062</v>
+        <v>0.03624069175545414</v>
       </c>
       <c r="W100">
-        <v>0.2271672453420646</v>
+        <v>0.2272544448840639</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2928839578604049</v>
+        <v>0.2899255340436332</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2502553456944748</v>
-      </c>
-      <c r="C101">
-        <v>-871.0282141325628</v>
-      </c>
-      <c r="D101">
-        <v>229.349785867437</v>
-      </c>
-      <c r="E101">
-        <v>487.7179999999998</v>
-      </c>
-      <c r="F101">
-        <v>1107.018</v>
-      </c>
-      <c r="G101">
-        <v>6.64</v>
-      </c>
-      <c r="H101">
-        <v>498.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>76.26666666666667</v>
-      </c>
-      <c r="K101">
-        <v>0.586</v>
-      </c>
-      <c r="L101">
-        <v>75.68066666666667</v>
-      </c>
-      <c r="M101">
-        <v>261.0348443999999</v>
-      </c>
-      <c r="N101">
-        <v>-185.3541777333333</v>
-      </c>
-      <c r="O101">
-        <v>-23.16927221666666</v>
-      </c>
-      <c r="P101">
-        <v>-162.1849055166666</v>
-      </c>
-      <c r="Q101">
-        <v>-161.5989055166666</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.527344525925154</v>
-      </c>
-      <c r="T101">
-        <v>48.36992170667842</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03624069175545414</v>
-      </c>
-      <c r="W101">
-        <v>0.2272544448840639</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2899255340436332</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
